--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2b07aacc79a2cf58/Documents/GitHub/Command-Line-Interface-Calculator/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="120" documentId="11_F25DC773A252ABDACC104830B9DC663C5BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7A4E590-CAF0-4EC2-89FD-FEE989F7C5F7}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,9 +24,101 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
+  <si>
+    <t>Functions</t>
+  </si>
+  <si>
+    <t>Parameters</t>
+  </si>
+  <si>
+    <t>Return</t>
+  </si>
+  <si>
+    <t>Addition</t>
+  </si>
+  <si>
+    <t>Subtraction</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Multiplication</t>
+  </si>
+  <si>
+    <t>Division</t>
+  </si>
+  <si>
+    <t>Modulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basic Operators </t>
+  </si>
+  <si>
+    <t>Area</t>
+  </si>
+  <si>
+    <t>Square</t>
+  </si>
+  <si>
+    <t>Rectangle</t>
+  </si>
+  <si>
+    <t>Circle</t>
+  </si>
+  <si>
+    <t>Triangle</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>Cube</t>
+  </si>
+  <si>
+    <t>Cuboid</t>
+  </si>
+  <si>
+    <t>Sphere</t>
+  </si>
+  <si>
+    <t>Cylinder</t>
+  </si>
+  <si>
+    <t>Sequences</t>
+  </si>
+  <si>
+    <t>Arithmetic sequence</t>
+  </si>
+  <si>
+    <t>Geometric sequence</t>
+  </si>
+  <si>
+    <t>Physics</t>
+  </si>
+  <si>
+    <t>Velocity</t>
+  </si>
+  <si>
+    <t>Projectiles</t>
+  </si>
+  <si>
+    <t>Unfinished</t>
+  </si>
+  <si>
+    <t>Description (function.py)</t>
+  </si>
+  <si>
+    <t>Descrtiption (main.py)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +126,42 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,18 +169,47 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFCC3300"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -330,10 +483,304 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
+  </sheetPr>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="25.21875" customWidth="1"/>
+    <col min="2" max="2" width="36.33203125" customWidth="1"/>
+    <col min="3" max="3" width="37.109375" customWidth="1"/>
+    <col min="4" max="4" width="29.109375" customWidth="1"/>
+    <col min="5" max="5" width="26.109375" customWidth="1"/>
+    <col min="6" max="6" width="29.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A21:F21"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2b07aacc79a2cf58/Documents/GitHub/Command-Line-Interface-Calculator/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e253c7f3c843a3b/Documents/GitHub/Command-Line-Interface-Calculator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="120" documentId="11_F25DC773A252ABDACC104830B9DC663C5BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7A4E590-CAF0-4EC2-89FD-FEE989F7C5F7}"/>
+  <xr:revisionPtr revIDLastSave="125" documentId="11_F25DC773A252ABDACC104830B9DC663C5BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A37A4BB-C408-4C26-88D7-906994EF44EF}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
   <si>
     <t>Functions</t>
   </si>
@@ -112,6 +112,9 @@
   </si>
   <si>
     <t>Descrtiption (main.py)</t>
+  </si>
+  <si>
+    <t>Un Finished</t>
   </si>
 </sst>
 </file>
@@ -188,17 +191,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -519,256 +521,256 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
     </row>
     <row r="3" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="4" t="s">
-        <v>26</v>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="4" t="s">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="4" t="s">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="4" t="s">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
     </row>
     <row r="9" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="5" t="s">
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="5" t="s">
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="5" t="s">
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="5" t="s">
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
     </row>
     <row r="14" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="5" t="s">
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="5" t="s">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="5" t="s">
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="5" t="s">
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
     </row>
     <row r="19" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="5" t="s">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="5" t="s">
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
     </row>
     <row r="22" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="5" t="s">
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="5" t="s">
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="3" t="s">
         <v>26</v>
       </c>
     </row>
@@ -780,6 +782,11 @@
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A21:F21"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F7 F9:F12 F14:F17 F19:F20 F22:F23" xr:uid="{7CD2734D-DB3A-4D87-9556-BF6DCAB974C0}">
+      <formula1>"Un Finished, Finished, In progress"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e253c7f3c843a3b/Documents/GitHub/Command-Line-Interface-Calculator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="125" documentId="11_F25DC773A252ABDACC104830B9DC663C5BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A37A4BB-C408-4C26-88D7-906994EF44EF}"/>
+  <xr:revisionPtr revIDLastSave="126" documentId="11_F25DC773A252ABDACC104830B9DC663C5BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5AB5E56-EEDF-4492-A217-E441AC58450D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -114,7 +114,7 @@
     <t>Descrtiption (main.py)</t>
   </si>
   <si>
-    <t>Un Finished</t>
+    <t>UnFinished</t>
   </si>
 </sst>
 </file>
@@ -205,10 +205,360 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="48">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF0000"/>
       <color rgb="FFCC3300"/>
     </mruColors>
   </colors>
@@ -551,7 +901,7 @@
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -563,7 +913,7 @@
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -575,7 +925,7 @@
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -587,7 +937,7 @@
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -609,7 +959,7 @@
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -621,7 +971,7 @@
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -633,7 +983,7 @@
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -645,7 +995,7 @@
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -667,7 +1017,7 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -679,7 +1029,7 @@
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -691,7 +1041,7 @@
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -703,7 +1053,7 @@
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -737,7 +1087,7 @@
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -771,7 +1121,7 @@
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -782,9 +1132,92 @@
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A21:F21"/>
   </mergeCells>
+  <conditionalFormatting sqref="F3:F7">
+    <cfRule type="containsText" dxfId="20" priority="21" operator="containsText" text="Un Finished">
+      <formula>NOT(ISERROR(SEARCH("Un Finished",F3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="21" priority="20" operator="containsText" text="Un Finished">
+      <formula>NOT(ISERROR(SEARCH("Un Finished",F3)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="19" operator="equal">
+      <formula>"Finished"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="23" priority="18" operator="equal">
+      <formula>"In Progress"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="17" operator="equal">
+      <formula>"In Progress"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="16" operator="equal">
+      <formula>"Un Finished"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="26" priority="15" operator="containsText" text="Un Finished">
+      <formula>NOT(ISERROR(SEARCH("Un Finished",F3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F9:F12">
+    <cfRule type="cellIs" dxfId="17" priority="14" operator="equal">
+      <formula>"Un Finished"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="13" operator="equal">
+      <formula>"Finished"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="12" operator="equal">
+      <formula>"In Progress"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14:F17">
+    <cfRule type="cellIs" dxfId="13" priority="11" operator="equal">
+      <formula>"Finished"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="10" operator="equal">
+      <formula>"In Progress"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19:F20">
+    <cfRule type="cellIs" dxfId="10" priority="9" operator="equal">
+      <formula>"Finished"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="8" operator="equal">
+      <formula>"In Progress"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22:F23">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
+      <formula>"Finished"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+      <formula>"In Progress"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F7">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"Active"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F9:F12">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"Active"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14:F17">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"Active"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19:F20">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"Active"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F22:F23">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"Active"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F7 F9:F12 F14:F17 F19:F20 F22:F23" xr:uid="{7CD2734D-DB3A-4D87-9556-BF6DCAB974C0}">
-      <formula1>"Un Finished, Finished, In progress"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F19:F20 F3:F7 F9:F12 F14:F17 F22:F23" xr:uid="{BA62F465-EA9B-4CE6-B8E2-0ED95EB31D25}">
+      <formula1>"UnFinished, Finished, Active"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e253c7f3c843a3b/Documents/GitHub/Command-Line-Interface-Calculator/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2b07aacc79a2cf58/Documents/GitHub/Command-Line-Interface-Calculator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="126" documentId="11_F25DC773A252ABDACC104830B9DC663C5BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5AB5E56-EEDF-4492-A217-E441AC58450D}"/>
+  <xr:revisionPtr revIDLastSave="334" documentId="11_F25DC773A252ABDACC104830B9DC663C5BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05BA9210-2FB2-4256-AF5C-6813C6EBA803}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="94">
   <si>
     <t>Functions</t>
   </si>
@@ -115,6 +115,290 @@
   </si>
   <si>
     <t>UnFinished</t>
+  </si>
+  <si>
+    <t>two parameters; both should be able to take float numbers.</t>
+  </si>
+  <si>
+    <t>should return the sum of the two numbers.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Must be used to add numbers </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">continously </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>as the user enters numbers. It must be used to add more then just two numbers.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Must be used to substract numbers </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>continously</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> as the user enters numbers. It must be used to subtract more then just two numbers.</t>
+    </r>
+  </si>
+  <si>
+    <t>two parameters; both should be able to take float numbers. It should be paramater1 - paramater2 not the otherway around.</t>
+  </si>
+  <si>
+    <t>should return the difference of the two numbers.</t>
+  </si>
+  <si>
+    <t>function to add two numbers. Function Name should be sum_of()</t>
+  </si>
+  <si>
+    <t>function to get the difference of two numbers. Function name should be difference_of()</t>
+  </si>
+  <si>
+    <t>function to get the product of two numbers. Function name should be product_of()</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Must be used to multiply numbers </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>continously</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> as the user enters numbers. It must be used to multiply more then just two numbers.</t>
+    </r>
+  </si>
+  <si>
+    <t>should return the product of the two numbers.</t>
+  </si>
+  <si>
+    <t>function to get the division of two numbers. Function name should be division_of()</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Must be used to divide numbers </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>continously</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> as the user enters numbers. It must be used to divide more then just two numbers. Remember dividing by zero is a error. Remember to handle it.</t>
+    </r>
+  </si>
+  <si>
+    <t>two parameters; both should be able to take float numbers. It should be paramater1 / paramater2 not the otherway around.</t>
+  </si>
+  <si>
+    <t>should return the division of the two numbers.</t>
+  </si>
+  <si>
+    <t>function to get the MOD of two numbers. Function name should be mod_of()</t>
+  </si>
+  <si>
+    <t>Must be used to get the modulus. In A MOD B, B should not be zero</t>
+  </si>
+  <si>
+    <t>two parameters; both should be able to take float numbers. It should be paramater1 MOD paramater2 not the otherway around.</t>
+  </si>
+  <si>
+    <t>should return the Modulus.</t>
+  </si>
+  <si>
+    <t>Function should take lenght of one side and square it.</t>
+  </si>
+  <si>
+    <t>one parameter for the length of the side. Should be able to take a float value</t>
+  </si>
+  <si>
+    <t>should return the area of the square</t>
+  </si>
+  <si>
+    <t>Function should take the length and the width of the rectangle  and return the product..</t>
+  </si>
+  <si>
+    <t>Ask the user for the length of one side. Output the area.</t>
+  </si>
+  <si>
+    <t>Ask the user for the length and width. Output the area.</t>
+  </si>
+  <si>
+    <t>two parameters, lenght and width. Should be able to take a float value.</t>
+  </si>
+  <si>
+    <t>should return the area of the rectangle</t>
+  </si>
+  <si>
+    <t>Ask the user for the radius. Output the area.</t>
+  </si>
+  <si>
+    <t>one parameter for the radius. Should be able to take float values</t>
+  </si>
+  <si>
+    <t>should return the area of the circle</t>
+  </si>
+  <si>
+    <t>Function should take the radius only. And return the Area. Pi = 3.142</t>
+  </si>
+  <si>
+    <t>Function should take base length and height.</t>
+  </si>
+  <si>
+    <t>Ask the user for the base length and height. Output the area.</t>
+  </si>
+  <si>
+    <t>two parameters, base length and height. Should be able to take float values.</t>
+  </si>
+  <si>
+    <t>should return the area of the triangle</t>
+  </si>
+  <si>
+    <t>Function should take lenght of one side and cube it.</t>
+  </si>
+  <si>
+    <t>Ask the user for the length of one side. Output the volume.</t>
+  </si>
+  <si>
+    <t>Function should take the length , the width and the height of the cuboid and return the volume..</t>
+  </si>
+  <si>
+    <t>Ask the user for the length, width and height. Output the volume.</t>
+  </si>
+  <si>
+    <t>three parameters, lengtht, width and height. Should be able to take a float value.</t>
+  </si>
+  <si>
+    <t>should return the volume of the cube.</t>
+  </si>
+  <si>
+    <t>should return the volume of the cuboid.</t>
+  </si>
+  <si>
+    <t>Function should take the radius only. And return the volume. Pi = 3.142</t>
+  </si>
+  <si>
+    <t>Ask the user for the radius. Output the volume.</t>
+  </si>
+  <si>
+    <t>should return the volume of the sphere.</t>
+  </si>
+  <si>
+    <t>Function should take the radius and height. And return the volume. Pi = 3.142</t>
+  </si>
+  <si>
+    <t>Ask the user for the radius and height. Output the volume.</t>
+  </si>
+  <si>
+    <t>two parameter for the radius and height. Should be able to take float values</t>
+  </si>
+  <si>
+    <t>should return the volume of the cylinder.</t>
+  </si>
+  <si>
+    <t>Function to find the nth term. Should take first term and common difference</t>
+  </si>
+  <si>
+    <t>three parameters, common difference, first element and n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ask the user for the sequence and how many more elements are required. Find the common difference, and the starting number, print the sequence till the nth term. The sequence must have more then 1 elements. n must be an integer. Input must be taken with commas ex:- 1,3,5,6 </t>
+  </si>
+  <si>
+    <t>should return nth element</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ask the user for the sequence and how many more elements are required. Find the common ratio, and the starting number, print the sequence till the nth term. The sequence must have more then 1 elements. n must be an integer. Input must be taken with commas ex:- 1,3,5,6 </t>
+  </si>
+  <si>
+    <t>three parameters, common ratio, first element and n</t>
+  </si>
+  <si>
+    <t>Function to find the nth term.  Should take first term and common ratio</t>
+  </si>
+  <si>
+    <t>function should take distance and time, distance is taken as meters and time as seconds</t>
+  </si>
+  <si>
+    <t>two parameters, time and distance</t>
+  </si>
+  <si>
+    <t>should return the velocity</t>
+  </si>
+  <si>
+    <t>remember to ask the user for the time in seconds and distance in meters. When outputing it should be answer: xxx m/s</t>
+  </si>
+  <si>
+    <t>function should take the velocity and the angle, ms-1 and Degree (angle) °. And return the maximum height and the distance it traveled</t>
+  </si>
+  <si>
+    <t>ask the user for the velocity in ms-1 and angle in degrees, output should be max height and distance it travels</t>
+  </si>
+  <si>
+    <t>two parameters, angle and velocity</t>
+  </si>
+  <si>
+    <t>return the maximum height and the distance it traveled</t>
   </si>
 </sst>
 </file>
@@ -191,21 +475,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="48">
+  <dxfs count="21">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -223,6 +521,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
@@ -237,6 +542,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
@@ -244,6 +556,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
@@ -258,91 +584,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -402,155 +644,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -843,9 +937,9 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.21875" customWidth="1"/>
-    <col min="2" max="2" width="36.33203125" customWidth="1"/>
-    <col min="3" max="3" width="37.109375" customWidth="1"/>
-    <col min="4" max="4" width="29.109375" customWidth="1"/>
+    <col min="2" max="2" width="44.5546875" customWidth="1"/>
+    <col min="3" max="3" width="61.6640625" customWidth="1"/>
+    <col min="4" max="4" width="49.5546875" customWidth="1"/>
     <col min="5" max="5" width="26.109375" customWidth="1"/>
     <col min="6" max="6" width="29.44140625" customWidth="1"/>
   </cols>
@@ -870,257 +964,393 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-    </row>
-    <row r="3" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="3" t="s">
+      <c r="B3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="3" t="s">
+      <c r="B4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="3" t="s">
+      <c r="B5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:6" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="3" t="s">
+      <c r="B6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="3" t="s">
+      <c r="B7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+    </row>
+    <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="3" t="s">
+      <c r="B9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="3" t="s">
+      <c r="B10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="3" t="s">
+      <c r="B11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="3" t="s">
+      <c r="B12" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+    </row>
+    <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="3" t="s">
+      <c r="B14" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="3" t="s">
+      <c r="B15" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+    <row r="16" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="3" t="s">
+      <c r="B16" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="3" t="s">
+      <c r="B17" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+    <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-    </row>
-    <row r="19" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+    </row>
+    <row r="19" spans="1:6" ht="73.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="3" t="s">
+      <c r="B19" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="3" t="s">
+      <c r="B20" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
+    <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-    </row>
-    <row r="22" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+    </row>
+    <row r="22" spans="1:6" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="3" t="s">
+      <c r="B22" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+    <row r="23" spans="1:6" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="3" t="s">
+      <c r="B23" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1133,86 +1363,76 @@
     <mergeCell ref="A21:F21"/>
   </mergeCells>
   <conditionalFormatting sqref="F3:F7">
-    <cfRule type="containsText" dxfId="20" priority="21" operator="containsText" text="Un Finished">
+    <cfRule type="cellIs" dxfId="20" priority="5" operator="equal">
+      <formula>"Active"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="19" priority="15" operator="containsText" text="Un Finished">
       <formula>NOT(ISERROR(SEARCH("Un Finished",F3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="20" operator="containsText" text="Un Finished">
+    <cfRule type="cellIs" dxfId="18" priority="16" operator="equal">
+      <formula>"Un Finished"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="17" priority="17" operator="equal">
+      <formula>"In Progress"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="18" operator="equal">
+      <formula>"In Progress"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="19" operator="equal">
+      <formula>"Finished"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="14" priority="20" operator="containsText" text="Un Finished">
       <formula>NOT(ISERROR(SEARCH("Un Finished",F3)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="19" operator="equal">
-      <formula>"Finished"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="18" operator="equal">
-      <formula>"In Progress"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="17" operator="equal">
-      <formula>"In Progress"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="16" operator="equal">
-      <formula>"Un Finished"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="15" operator="containsText" text="Un Finished">
+    <cfRule type="containsText" dxfId="13" priority="21" operator="containsText" text="Un Finished">
       <formula>NOT(ISERROR(SEARCH("Un Finished",F3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:F12">
-    <cfRule type="cellIs" dxfId="17" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="4" operator="equal">
+      <formula>"Active"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
+      <formula>"In Progress"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="13" operator="equal">
+      <formula>"Finished"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="14" operator="equal">
       <formula>"Un Finished"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="13" operator="equal">
-      <formula>"Finished"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="12" operator="equal">
-      <formula>"In Progress"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14:F17">
-    <cfRule type="cellIs" dxfId="13" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
+      <formula>"Active"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="10" operator="equal">
+      <formula>"In Progress"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="11" operator="equal">
       <formula>"Finished"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="10" operator="equal">
-      <formula>"In Progress"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19:F20">
-    <cfRule type="cellIs" dxfId="10" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+      <formula>"Active"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
+      <formula>"In Progress"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="9" operator="equal">
       <formula>"Finished"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="8" operator="equal">
-      <formula>"In Progress"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F22:F23">
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"Active"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
+      <formula>"In Progress"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
       <formula>"Finished"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
-      <formula>"In Progress"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F7">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
-      <formula>"Active"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9:F12">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
-      <formula>"Active"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F14:F17">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"Active"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F19:F20">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"Active"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F22:F23">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>"Active"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2b07aacc79a2cf58/Documents/GitHub/Command-Line-Interface-Calculator/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e253c7f3c843a3b/Documents/GitHub/Command-Line-Interface-Calculator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="334" documentId="11_F25DC773A252ABDACC104830B9DC663C5BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05BA9210-2FB2-4256-AF5C-6813C6EBA803}"/>
+  <xr:revisionPtr revIDLastSave="337" documentId="11_F25DC773A252ABDACC104830B9DC663C5BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A29AA39-6C9A-455F-956E-C3C5EABFE3C4}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Descriptions" sheetId="1" r:id="rId1"/>
+    <sheet name="Parameters" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="174">
   <si>
     <t>Functions</t>
   </si>
@@ -400,12 +401,252 @@
   <si>
     <t>return the maximum height and the distance it traveled</t>
   </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Function Name</t>
+  </si>
+  <si>
+    <t>Data Type</t>
+  </si>
+  <si>
+    <t>Formula / Logic</t>
+  </si>
+  <si>
+    <t>Return Value</t>
+  </si>
+  <si>
+    <t>Validation / Errors</t>
+  </si>
+  <si>
+    <t>Assigned To</t>
+  </si>
+  <si>
+    <t>Basic</t>
+  </si>
+  <si>
+    <t>addition()</t>
+  </si>
+  <si>
+    <t>num1 + num2</t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
+  <si>
+    <t>Must be numbers</t>
+  </si>
+  <si>
+    <t>subtraction()</t>
+  </si>
+  <si>
+    <t>num1 - num2</t>
+  </si>
+  <si>
+    <t>Difference</t>
+  </si>
+  <si>
+    <t>circle()</t>
+  </si>
+  <si>
+    <t>3.142 × r²</t>
+  </si>
+  <si>
+    <t>radius &gt; 0</t>
+  </si>
+  <si>
+    <t>velocity()</t>
+  </si>
+  <si>
+    <t>distance / time</t>
+  </si>
+  <si>
+    <t>time ≠ 0</t>
+  </si>
+  <si>
+    <t>Multiplication()</t>
+  </si>
+  <si>
+    <t>Division()</t>
+  </si>
+  <si>
+    <t>Modulus()</t>
+  </si>
+  <si>
+    <t>num1  * num2</t>
+  </si>
+  <si>
+    <t>num1  / num2</t>
+  </si>
+  <si>
+    <t>num1 mod num2</t>
+  </si>
+  <si>
+    <t>num1, num2 …....</t>
+  </si>
+  <si>
+    <t>Must be numbers. Input value&gt;0</t>
+  </si>
+  <si>
+    <t>Quotient of the two numbers</t>
+  </si>
+  <si>
+    <t>Remainder</t>
+  </si>
+  <si>
+    <t>square()</t>
+  </si>
+  <si>
+    <t>side</t>
+  </si>
+  <si>
+    <t>side²</t>
+  </si>
+  <si>
+    <t>Area of square</t>
+  </si>
+  <si>
+    <t>side &gt; 0</t>
+  </si>
+  <si>
+    <t>rectangle()</t>
+  </si>
+  <si>
+    <t>Area of rectangle</t>
+  </si>
+  <si>
+    <t>Values &gt; 0</t>
+  </si>
+  <si>
+    <t>Area of circle</t>
+  </si>
+  <si>
+    <t>triangle()</t>
+  </si>
+  <si>
+    <t>Area of triangle</t>
+  </si>
+  <si>
+    <t>cube()</t>
+  </si>
+  <si>
+    <t>side³</t>
+  </si>
+  <si>
+    <t>Volume of cube</t>
+  </si>
+  <si>
+    <t>cuboid()</t>
+  </si>
+  <si>
+    <t>l × w × h</t>
+  </si>
+  <si>
+    <t>Volume of cuboid</t>
+  </si>
+  <si>
+    <t>sphere()</t>
+  </si>
+  <si>
+    <t>4/3 × 3.142 × r³</t>
+  </si>
+  <si>
+    <t>Volume of sphere</t>
+  </si>
+  <si>
+    <t>cylinder()</t>
+  </si>
+  <si>
+    <t>3.142 × r² × h</t>
+  </si>
+  <si>
+    <t>Volume of cylinder</t>
+  </si>
+  <si>
+    <t>l , w</t>
+  </si>
+  <si>
+    <t>r</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> b , h</t>
+  </si>
+  <si>
+    <t>l, w, h</t>
+  </si>
+  <si>
+    <t>r, h</t>
+  </si>
+  <si>
+    <t>½ × b × h</t>
+  </si>
+  <si>
+    <t>l × w</t>
+  </si>
+  <si>
+    <t>Sequence</t>
+  </si>
+  <si>
+    <t>arithmetic_sequence()</t>
+  </si>
+  <si>
+    <t>float/int</t>
+  </si>
+  <si>
+    <t>a + (n-1)d</t>
+  </si>
+  <si>
+    <t>nth term</t>
+  </si>
+  <si>
+    <t>n &gt; 0</t>
+  </si>
+  <si>
+    <t>geometric_sequence()</t>
+  </si>
+  <si>
+    <t>a × rⁿ⁻¹</t>
+  </si>
+  <si>
+    <t>a, d, n</t>
+  </si>
+  <si>
+    <t>a, r, n</t>
+  </si>
+  <si>
+    <t>projectiles()</t>
+  </si>
+  <si>
+    <t>According to requirement</t>
+  </si>
+  <si>
+    <t>Projectile formula</t>
+  </si>
+  <si>
+    <t>Projectile result</t>
+  </si>
+  <si>
+    <t>Validate inputs</t>
+  </si>
+  <si>
+    <t>d, t</t>
+  </si>
+  <si>
+    <t>Parameters/Variable Name</t>
+  </si>
+  <si>
+    <t>Basic Operation</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -421,8 +662,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -447,8 +699,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -471,17 +735,102 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -490,13 +839,299 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="44">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -934,7 +1569,7 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="25.21875" customWidth="1"/>
     <col min="2" max="2" width="44.5546875" customWidth="1"/>
@@ -944,7 +1579,7 @@
     <col min="6" max="6" width="29.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="46.8" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -964,117 +1599,117 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:6" ht="30" customHeight="1">
+      <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6" ht="30" customHeight="1">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:6" ht="42" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:6" ht="30" customHeight="1">
+      <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:6" ht="48.6" customHeight="1">
+      <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:6" ht="48" customHeight="1">
+      <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="30" customHeight="1">
       <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
@@ -1084,87 +1719,87 @@
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
     </row>
-    <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:6" ht="30" customHeight="1">
+      <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:6" ht="30" customHeight="1">
+      <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:6" ht="30" customHeight="1">
+      <c r="A11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:6" ht="30" customHeight="1">
+      <c r="A12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="30" customHeight="1">
       <c r="A13" s="5" t="s">
         <v>15</v>
       </c>
@@ -1174,87 +1809,87 @@
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
     </row>
-    <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:6" ht="30" customHeight="1">
+      <c r="A14" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+    <row r="15" spans="1:6" ht="30" customHeight="1">
+      <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:6" ht="30" customHeight="1">
+      <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+    <row r="17" spans="1:6" ht="30" customHeight="1">
+      <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="30" customHeight="1">
       <c r="A18" s="5" t="s">
         <v>20</v>
       </c>
@@ -1264,47 +1899,47 @@
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
     </row>
-    <row r="19" spans="1:6" ht="73.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+    <row r="19" spans="1:6" ht="73.2" customHeight="1">
+      <c r="A19" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="78" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
+    <row r="20" spans="1:6" ht="78" customHeight="1">
+      <c r="A20" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="30" customHeight="1">
       <c r="A21" s="5" t="s">
         <v>23</v>
       </c>
@@ -1314,43 +1949,43 @@
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
     </row>
-    <row r="22" spans="1:6" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
+    <row r="22" spans="1:6" ht="52.2" customHeight="1">
+      <c r="A22" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+    <row r="23" spans="1:6" ht="43.8" customHeight="1">
+      <c r="A23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="3" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1363,75 +1998,75 @@
     <mergeCell ref="A21:F21"/>
   </mergeCells>
   <conditionalFormatting sqref="F3:F7">
-    <cfRule type="cellIs" dxfId="20" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="5" operator="equal">
       <formula>"Active"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="19" priority="15" operator="containsText" text="Un Finished">
+    <cfRule type="containsText" dxfId="42" priority="15" operator="containsText" text="Un Finished">
       <formula>NOT(ISERROR(SEARCH("Un Finished",F3)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="16" operator="equal">
       <formula>"Un Finished"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="17" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="18" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="19" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="20" operator="containsText" text="Un Finished">
+    <cfRule type="containsText" dxfId="37" priority="20" operator="containsText" text="Un Finished">
       <formula>NOT(ISERROR(SEARCH("Un Finished",F3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="21" operator="containsText" text="Un Finished">
+    <cfRule type="containsText" dxfId="36" priority="21" operator="containsText" text="Un Finished">
       <formula>NOT(ISERROR(SEARCH("Un Finished",F3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:F12">
-    <cfRule type="cellIs" dxfId="12" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="4" operator="equal">
       <formula>"Active"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="12" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="13" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="14" operator="equal">
       <formula>"Un Finished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14:F17">
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="3" operator="equal">
       <formula>"Active"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="10" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="11" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19:F20">
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="2" operator="equal">
       <formula>"Active"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="8" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="9" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F22:F23">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>"Active"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="6" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="7" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1443,4 +2078,812 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{704ADD10-B33C-4154-819F-B6544A981113}">
+  <dimension ref="A1:M28"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" customWidth="1"/>
+    <col min="4" max="4" width="18.77734375" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" customWidth="1"/>
+    <col min="7" max="7" width="24.77734375" customWidth="1"/>
+    <col min="8" max="8" width="22.88671875" customWidth="1"/>
+    <col min="9" max="9" width="18.33203125" customWidth="1"/>
+    <col min="10" max="10" width="11.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="30" customHeight="1">
+      <c r="A1" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="18"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="19"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="21"/>
+      <c r="L3" s="6"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="22">
+        <v>1</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4" s="6"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="22">
+        <v>2</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="22">
+        <v>3</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="28.8">
+      <c r="A7" s="22">
+        <v>4</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="23">
+        <v>5</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="I8" s="13"/>
+      <c r="J8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="19"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="24">
+        <v>6</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="22">
+        <v>7</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I12" s="7"/>
+      <c r="J12" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="22">
+        <v>8</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="I13" s="7"/>
+      <c r="J13" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="22">
+        <v>9</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I14" s="7"/>
+      <c r="J14" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="19"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="22">
+        <v>10</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I17" s="9"/>
+      <c r="J17" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="22">
+        <v>11</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I18" s="9"/>
+      <c r="J18" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="22">
+        <v>12</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="I19" s="9"/>
+      <c r="J19" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="22">
+        <v>13</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I20" s="9"/>
+      <c r="J20" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="18"/>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="19"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="21"/>
+    </row>
+    <row r="23" spans="1:13" ht="26.4">
+      <c r="A23" s="22">
+        <v>14</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="I23" s="9"/>
+      <c r="J23" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="26.4">
+      <c r="A24" s="22">
+        <v>15</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="I24" s="9"/>
+      <c r="J24" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="18"/>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="19"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="21"/>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="22">
+        <v>16</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="I27" s="9"/>
+      <c r="J27" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="28.8">
+      <c r="A28" s="22">
+        <v>17</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="I28" s="9"/>
+      <c r="J28" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A2:J3"/>
+    <mergeCell ref="A9:J10"/>
+    <mergeCell ref="A15:J16"/>
+    <mergeCell ref="A21:J22"/>
+    <mergeCell ref="A25:J26"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="J4:J8 J11:J14 J17:J20 J23:J24 J27:J28">
+    <cfRule type="cellIs" dxfId="20" priority="12" operator="equal">
+      <formula>"Unfinished"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="13" operator="equal">
+      <formula>"Finished"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="14" operator="equal">
+      <formula>"Finished"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J4:J8">
+    <cfRule type="cellIs" dxfId="17" priority="11" operator="equal">
+      <formula>"Unfinished"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="10" operator="equal">
+      <formula>"Finished"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J11:J14">
+    <cfRule type="cellIs" dxfId="15" priority="9" operator="equal">
+      <formula>"Unfinished"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="8" operator="equal">
+      <formula>"Finished"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J17:J20 J23:J24 J27:J28">
+    <cfRule type="iconSet" priority="7">
+      <iconSet iconSet="3Symbols">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+      <formula>"Unfinished"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
+      <formula>"Finished"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J17:J20">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"Finished"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J23:J24">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"Finished"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J23:J24">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"Finished"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J27:J28">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"Finished"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J23:J24 J4:J8 J11:J14 J17:J20 J27:J28" xr:uid="{7712DC73-C9ED-4AE1-A76C-20335CA8FDA5}">
+      <formula1>"Finished, Unfinished"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e253c7f3c843a3b/Documents/GitHub/Command-Line-Interface-Calculator/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2b07aacc79a2cf58/Documents/GitHub/Command-Line-Interface-Calculator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="337" documentId="11_F25DC773A252ABDACC104830B9DC663C5BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A29AA39-6C9A-455F-956E-C3C5EABFE3C4}"/>
+  <xr:revisionPtr revIDLastSave="370" documentId="11_F25DC773A252ABDACC104830B9DC663C5BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{428963B3-6F8E-4A13-988A-9275D238629B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptions" sheetId="1" r:id="rId1"/>
@@ -369,9 +369,6 @@
     <t>should return nth element</t>
   </si>
   <si>
-    <t xml:space="preserve">ask the user for the sequence and how many more elements are required. Find the common ratio, and the starting number, print the sequence till the nth term. The sequence must have more then 1 elements. n must be an integer. Input must be taken with commas ex:- 1,3,5,6 </t>
-  </si>
-  <si>
     <t>three parameters, common ratio, first element and n</t>
   </si>
   <si>
@@ -450,12 +447,6 @@
     <t>Difference</t>
   </si>
   <si>
-    <t>circle()</t>
-  </si>
-  <si>
-    <t>3.142 × r²</t>
-  </si>
-  <si>
     <t>radius &gt; 0</t>
   </si>
   <si>
@@ -498,9 +489,6 @@
     <t>Remainder</t>
   </si>
   <si>
-    <t>square()</t>
-  </si>
-  <si>
     <t>side</t>
   </si>
   <si>
@@ -513,9 +501,6 @@
     <t>side &gt; 0</t>
   </si>
   <si>
-    <t>rectangle()</t>
-  </si>
-  <si>
     <t>Area of rectangle</t>
   </si>
   <si>
@@ -525,69 +510,24 @@
     <t>Area of circle</t>
   </si>
   <si>
-    <t>triangle()</t>
-  </si>
-  <si>
     <t>Area of triangle</t>
   </si>
   <si>
-    <t>cube()</t>
-  </si>
-  <si>
     <t>side³</t>
   </si>
   <si>
     <t>Volume of cube</t>
   </si>
   <si>
-    <t>cuboid()</t>
-  </si>
-  <si>
-    <t>l × w × h</t>
-  </si>
-  <si>
     <t>Volume of cuboid</t>
   </si>
   <si>
-    <t>sphere()</t>
-  </si>
-  <si>
-    <t>4/3 × 3.142 × r³</t>
-  </si>
-  <si>
     <t>Volume of sphere</t>
   </si>
   <si>
-    <t>cylinder()</t>
-  </si>
-  <si>
-    <t>3.142 × r² × h</t>
-  </si>
-  <si>
     <t>Volume of cylinder</t>
   </si>
   <si>
-    <t>l , w</t>
-  </si>
-  <si>
-    <t>r</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> b , h</t>
-  </si>
-  <si>
-    <t>l, w, h</t>
-  </si>
-  <si>
-    <t>r, h</t>
-  </si>
-  <si>
-    <t>½ × b × h</t>
-  </si>
-  <si>
-    <t>l × w</t>
-  </si>
-  <si>
     <t>Sequence</t>
   </si>
   <si>
@@ -618,9 +558,6 @@
     <t>a, r, n</t>
   </si>
   <si>
-    <t>projectiles()</t>
-  </si>
-  <si>
     <t>According to requirement</t>
   </si>
   <si>
@@ -633,13 +570,76 @@
     <t>Validate inputs</t>
   </si>
   <si>
-    <t>d, t</t>
-  </si>
-  <si>
     <t>Parameters/Variable Name</t>
   </si>
   <si>
     <t>Basic Operation</t>
+  </si>
+  <si>
+    <t>area_square()</t>
+  </si>
+  <si>
+    <t>area_rectangle()</t>
+  </si>
+  <si>
+    <t>area_circle()</t>
+  </si>
+  <si>
+    <t>area_triangle()</t>
+  </si>
+  <si>
+    <t>volume_cube()</t>
+  </si>
+  <si>
+    <t>volume_cuboid()</t>
+  </si>
+  <si>
+    <t>volume_sphere()</t>
+  </si>
+  <si>
+    <t>volume_cylinder()</t>
+  </si>
+  <si>
+    <t>ask the user for the sequence and how many more elements are required. Find the common ratio, and the starting number, print the sequence till the nth term. The sequence must have more then 1 elements. n must be an integer. Input must be taken with commas ex:- 1,3,9,27</t>
+  </si>
+  <si>
+    <t>length , width</t>
+  </si>
+  <si>
+    <t>radius</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> base , height</t>
+  </si>
+  <si>
+    <t>length, width, height</t>
+  </si>
+  <si>
+    <t>radius, height</t>
+  </si>
+  <si>
+    <t>distance, time</t>
+  </si>
+  <si>
+    <t>½ × base × height</t>
+  </si>
+  <si>
+    <t>3.142 × radius²</t>
+  </si>
+  <si>
+    <t>length × width</t>
+  </si>
+  <si>
+    <t>length × width × height</t>
+  </si>
+  <si>
+    <t>4/3 × 3.142 × radius³</t>
+  </si>
+  <si>
+    <t>3.142 × radius² × height</t>
+  </si>
+  <si>
+    <t>projectile()</t>
   </si>
 </sst>
 </file>
@@ -835,15 +835,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -870,6 +861,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -888,20 +894,14 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="44">
+  <dxfs count="34">
     <dxf>
       <font>
         <b/>
@@ -916,18 +916,18 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <b/>
         <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
       </font>
       <fill>
         <patternFill>
@@ -951,18 +951,6 @@
       <font>
         <b/>
         <i val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
       </font>
       <fill>
         <patternFill>
@@ -990,7 +978,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FF00B050"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1002,7 +990,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1014,7 +1002,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FF00B050"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1026,7 +1014,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1044,93 +1032,6 @@
       <font>
         <color rgb="FFFF0000"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -1600,14 +1501,14 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -1625,7 +1526,7 @@
       <c r="E3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="24" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1645,7 +1546,7 @@
       <c r="E4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="24" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1665,7 +1566,7 @@
       <c r="E5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="24" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1685,7 +1586,7 @@
       <c r="E6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="24" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1705,19 +1606,19 @@
       <c r="E7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="24" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1">
       <c r="A9" s="2" t="s">
@@ -1735,7 +1636,7 @@
       <c r="E9" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="24" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1755,7 +1656,7 @@
       <c r="E10" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="24" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1775,7 +1676,7 @@
       <c r="E11" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="24" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1795,19 +1696,19 @@
       <c r="E12" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="24" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1">
       <c r="A14" s="2" t="s">
@@ -1825,7 +1726,7 @@
       <c r="E14" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="24" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1845,7 +1746,7 @@
       <c r="E15" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="24" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1865,7 +1766,7 @@
       <c r="E16" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="24" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1885,19 +1786,19 @@
       <c r="E17" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="24" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
     </row>
     <row r="19" spans="1:6" ht="73.2" customHeight="1">
       <c r="A19" s="2" t="s">
@@ -1915,7 +1816,7 @@
       <c r="E19" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="24" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1924,48 +1825,48 @@
         <v>22</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="24" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
     </row>
     <row r="22" spans="1:6" ht="52.2" customHeight="1">
       <c r="A22" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="24" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1974,18 +1875,18 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="24" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1998,75 +1899,75 @@
     <mergeCell ref="A21:F21"/>
   </mergeCells>
   <conditionalFormatting sqref="F3:F7">
-    <cfRule type="cellIs" dxfId="43" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="5" operator="equal">
       <formula>"Active"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="15" operator="containsText" text="Un Finished">
+    <cfRule type="containsText" dxfId="32" priority="15" operator="containsText" text="Un Finished">
       <formula>NOT(ISERROR(SEARCH("Un Finished",F3)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="16" operator="equal">
       <formula>"Un Finished"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="17" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="18" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="19" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="37" priority="20" operator="containsText" text="Un Finished">
+    <cfRule type="containsText" dxfId="27" priority="20" operator="containsText" text="Un Finished">
       <formula>NOT(ISERROR(SEARCH("Un Finished",F3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="21" operator="containsText" text="Un Finished">
+    <cfRule type="containsText" dxfId="26" priority="21" operator="containsText" text="Un Finished">
       <formula>NOT(ISERROR(SEARCH("Un Finished",F3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:F12">
-    <cfRule type="cellIs" dxfId="35" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="4" operator="equal">
       <formula>"Active"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="12" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="13" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="14" operator="equal">
       <formula>"Un Finished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14:F17">
-    <cfRule type="cellIs" dxfId="31" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="3" operator="equal">
       <formula>"Active"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="10" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="11" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19:F20">
-    <cfRule type="cellIs" dxfId="28" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
       <formula>"Active"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="8" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="9" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F22:F23">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
       <formula>"Active"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="6" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2089,7 +1990,7 @@
     <col min="3" max="3" width="15.6640625" customWidth="1"/>
     <col min="4" max="4" width="18.77734375" customWidth="1"/>
     <col min="5" max="5" width="13.5546875" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" customWidth="1"/>
+    <col min="6" max="6" width="19.77734375" customWidth="1"/>
     <col min="7" max="7" width="24.77734375" customWidth="1"/>
     <col min="8" max="8" width="22.88671875" customWidth="1"/>
     <col min="9" max="9" width="18.33203125" customWidth="1"/>
@@ -2097,714 +1998,714 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="30" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="C1" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="D1" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="F1" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="20"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="21"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="23"/>
+      <c r="L3" s="3"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="13">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4" s="3"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="13">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="13">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="28.8">
+      <c r="A7" s="13">
+        <v>4</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="14">
+        <v>5</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="I8" s="10"/>
+      <c r="J8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="21"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="15">
+        <v>6</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="13">
+        <v>7</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="I12" s="4"/>
+      <c r="J12" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="13">
+        <v>8</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="I13" s="4"/>
+      <c r="J13" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="13">
+        <v>9</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="I14" s="4"/>
+      <c r="J14" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="21"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="13">
+        <v>10</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="I17" s="6"/>
+      <c r="J17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="1:13" ht="28.8">
+      <c r="A18" s="13">
+        <v>11</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="I18" s="6"/>
+      <c r="J18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="13">
+        <v>12</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="I19" s="6"/>
+      <c r="J19" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="28.8">
+      <c r="A20" s="13">
+        <v>13</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="E1" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="16" t="s">
+      <c r="G20" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="I20" s="6"/>
+      <c r="J20" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="20"/>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="21"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="23"/>
+    </row>
+    <row r="23" spans="1:13" ht="26.4">
+      <c r="A23" s="13">
+        <v>14</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I23" s="6"/>
+      <c r="J23" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="26.4">
+      <c r="A24" s="13">
+        <v>15</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="I24" s="6"/>
+      <c r="J24" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="20"/>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="21"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="23"/>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="13">
+        <v>16</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="I27" s="6"/>
+      <c r="J27" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="28.8">
+      <c r="A28" s="13">
+        <v>17</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="18"/>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="19"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="21"/>
-      <c r="L3" s="6"/>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="22">
-        <v>1</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="L4" s="6"/>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="22">
-        <v>2</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="22">
-        <v>3</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="28.8">
-      <c r="A7" s="22">
-        <v>4</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="23">
-        <v>5</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="I8" s="13"/>
-      <c r="J8" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="19"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="24">
-        <v>6</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="22">
-        <v>7</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="D12" s="7" t="s">
+      <c r="D28" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="H28" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I12" s="7"/>
-      <c r="J12" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="22">
-        <v>8</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="I13" s="7"/>
-      <c r="J13" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="22">
-        <v>9</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I14" s="7"/>
-      <c r="J14" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" s="19"/>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="22">
-        <v>10</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="I17" s="9"/>
-      <c r="J17" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-    </row>
-    <row r="18" spans="1:13">
-      <c r="A18" s="22">
-        <v>11</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I18" s="9"/>
-      <c r="J18" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-    </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="22">
-        <v>12</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="I19" s="9"/>
-      <c r="J19" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="22">
-        <v>13</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I20" s="9"/>
-      <c r="J20" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="A21" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="18"/>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="19"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="21"/>
-    </row>
-    <row r="23" spans="1:13" ht="26.4">
-      <c r="A23" s="22">
-        <v>14</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="I23" s="9"/>
-      <c r="J23" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="26.4">
-      <c r="A24" s="22">
-        <v>15</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="I24" s="9"/>
-      <c r="J24" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="A25" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="18"/>
-    </row>
-    <row r="26" spans="1:13">
-      <c r="A26" s="19"/>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="21"/>
-    </row>
-    <row r="27" spans="1:13">
-      <c r="A27" s="22">
-        <v>16</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="I27" s="9"/>
-      <c r="J27" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="28.8">
-      <c r="A28" s="22">
-        <v>17</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="I28" s="9"/>
-      <c r="J28" s="7" t="s">
+      <c r="I28" s="6"/>
+      <c r="J28" s="4" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2818,33 +2719,36 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="J4:J8 J11:J14 J17:J20 J23:J24 J27:J28">
-    <cfRule type="cellIs" dxfId="20" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="12" operator="equal">
       <formula>"Unfinished"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="13" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="14" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:J8">
-    <cfRule type="cellIs" dxfId="17" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
+      <formula>"Finished"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
       <formula>"Unfinished"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="10" operator="equal">
-      <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11:J14">
-    <cfRule type="cellIs" dxfId="15" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+      <formula>"Finished"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
       <formula>"Unfinished"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="8" operator="equal">
-      <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J17:J20 J23:J24 J27:J28">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+      <formula>"Unfinished"</formula>
+    </cfRule>
     <cfRule type="iconSet" priority="7">
       <iconSet iconSet="3Symbols">
         <cfvo type="percent" val="0"/>
@@ -2852,10 +2756,9 @@
         <cfvo type="percent" val="67"/>
       </iconSet>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
-      <formula>"Unfinished"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J17:J20 J27:J28">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2865,12 +2768,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J23:J24">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J23:J24">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2b07aacc79a2cf58/Documents/GitHub/Command-Line-Interface-Calculator/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e253c7f3c843a3b/Documents/GitHub/Command-Line-Interface-Calculator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="370" documentId="11_F25DC773A252ABDACC104830B9DC663C5BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{428963B3-6F8E-4A13-988A-9275D238629B}"/>
+  <xr:revisionPtr revIDLastSave="374" documentId="11_F25DC773A252ABDACC104830B9DC663C5BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A9D893C-788F-4F13-A4C7-75BB0CE4D469}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptions" sheetId="1" r:id="rId1"/>
@@ -552,12 +552,6 @@
     <t>a × rⁿ⁻¹</t>
   </si>
   <si>
-    <t>a, d, n</t>
-  </si>
-  <si>
-    <t>a, r, n</t>
-  </si>
-  <si>
     <t>According to requirement</t>
   </si>
   <si>
@@ -640,6 +634,12 @@
   </si>
   <si>
     <t>projectile()</t>
+  </si>
+  <si>
+    <t>first_term, difference, n</t>
+  </si>
+  <si>
+    <t>first_term, ratio, n</t>
   </si>
 </sst>
 </file>
@@ -870,11 +870,8 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -894,8 +891,11 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1501,14 +1501,14 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -1526,7 +1526,7 @@
       <c r="E3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="16" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       <c r="E4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="F4" s="16" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       <c r="E5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="24" t="s">
+      <c r="F5" s="16" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       <c r="E6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="F6" s="16" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1606,19 +1606,19 @@
       <c r="E7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="24" t="s">
+      <c r="F7" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1">
       <c r="A9" s="2" t="s">
@@ -1636,7 +1636,7 @@
       <c r="E9" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F9" s="24" t="s">
+      <c r="F9" s="16" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
       <c r="E10" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F10" s="24" t="s">
+      <c r="F10" s="16" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
       <c r="E11" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="F11" s="24" t="s">
+      <c r="F11" s="16" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1696,19 +1696,19 @@
       <c r="E12" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F12" s="24" t="s">
+      <c r="F12" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1">
       <c r="A14" s="2" t="s">
@@ -1726,7 +1726,7 @@
       <c r="E14" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F14" s="24" t="s">
+      <c r="F14" s="16" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       <c r="E15" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F15" s="24" t="s">
+      <c r="F15" s="16" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       <c r="E16" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F16" s="24" t="s">
+      <c r="F16" s="16" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1786,19 +1786,19 @@
       <c r="E17" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F17" s="24" t="s">
+      <c r="F17" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
     </row>
     <row r="19" spans="1:6" ht="73.2" customHeight="1">
       <c r="A19" s="2" t="s">
@@ -1816,7 +1816,7 @@
       <c r="E19" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F19" s="24" t="s">
+      <c r="F19" s="16" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
         <v>84</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>83</v>
@@ -1836,19 +1836,19 @@
       <c r="E20" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F20" s="24" t="s">
+      <c r="F20" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
     </row>
     <row r="22" spans="1:6" ht="52.2" customHeight="1">
       <c r="A22" s="2" t="s">
@@ -1866,7 +1866,7 @@
       <c r="E22" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="F22" s="24" t="s">
+      <c r="F22" s="16" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1886,7 +1886,7 @@
       <c r="E23" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F23" s="24" t="s">
+      <c r="F23" s="16" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
         <v>95</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>96</v>
@@ -2030,30 +2030,30 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="20"/>
+      <c r="A2" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="19"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="21"/>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="23"/>
+      <c r="A3" s="20"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="22"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:13">
@@ -2216,33 +2216,33 @@
       <c r="M8" s="3"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="20"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="19"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="21"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="23"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="22"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -2255,7 +2255,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>123</v>
@@ -2288,16 +2288,16 @@
         <v>10</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>127</v>
@@ -2321,16 +2321,16 @@
         <v>10</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>129</v>
@@ -2354,16 +2354,16 @@
         <v>10</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>130</v>
@@ -2380,33 +2380,33 @@
       <c r="M14" s="3"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="20"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="19"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="21"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="23"/>
+      <c r="A16" s="20"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="22"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -2419,7 +2419,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>123</v>
@@ -2444,7 +2444,7 @@
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
     </row>
-    <row r="18" spans="1:13" ht="28.8">
+    <row r="18" spans="1:13">
       <c r="A18" s="13">
         <v>11</v>
       </c>
@@ -2452,16 +2452,16 @@
         <v>15</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>133</v>
@@ -2485,16 +2485,16 @@
         <v>15</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>134</v>
@@ -2515,16 +2515,16 @@
         <v>15</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>135</v>
@@ -2538,32 +2538,32 @@
       </c>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="20"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="19"/>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="21"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="23"/>
-    </row>
-    <row r="23" spans="1:13" ht="26.4">
+      <c r="A22" s="20"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="22"/>
+    </row>
+    <row r="23" spans="1:13" ht="28.8">
       <c r="A23" s="13">
         <v>14</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>137</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>138</v>
@@ -2604,7 +2604,7 @@
         <v>142</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>145</v>
+        <v>173</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>138</v>
@@ -2624,30 +2624,30 @@
       </c>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="20"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="19"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="21"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="23"/>
+      <c r="A26" s="20"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="22"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="13">
@@ -2660,7 +2660,7 @@
         <v>110</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>138</v>
@@ -2687,22 +2687,22 @@
         <v>23</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F28" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="H28" s="4" t="s">
         <v>147</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>149</v>
       </c>
       <c r="I28" s="6"/>
       <c r="J28" s="4" t="s">

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e253c7f3c843a3b/Documents/GitHub/Command-Line-Interface-Calculator/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b1516d80b1b550f1/Documents/GitHub/Command-Line-Interface-Calculator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="374" documentId="11_F25DC773A252ABDACC104830B9DC663C5BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A9D893C-788F-4F13-A4C7-75BB0CE4D469}"/>
+  <xr:revisionPtr revIDLastSave="378" documentId="11_F25DC773A252ABDACC104830B9DC663C5BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BD51940-C1D9-4B12-A38C-F315D6F9A8CE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptions" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="175">
   <si>
     <t>Functions</t>
   </si>
@@ -640,6 +640,9 @@
   </si>
   <si>
     <t>first_term, ratio, n</t>
+  </si>
+  <si>
+    <t>Active</t>
   </si>
 </sst>
 </file>
@@ -873,6 +876,12 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -890,12 +899,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1501,14 +1504,14 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -1567,7 +1570,7 @@
         <v>40</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>29</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="48.6" customHeight="1">
@@ -1611,14 +1614,14 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="24"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1">
       <c r="A9" s="2" t="s">
@@ -1701,14 +1704,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1">
       <c r="A14" s="2" t="s">
@@ -1791,14 +1794,14 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
     </row>
     <row r="19" spans="1:6" ht="73.2" customHeight="1">
       <c r="A19" s="2" t="s">
@@ -1841,14 +1844,14 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
-      <c r="A21" s="24" t="s">
+      <c r="A21" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
     </row>
     <row r="22" spans="1:6" ht="52.2" customHeight="1">
       <c r="A22" s="2" t="s">
@@ -2030,30 +2033,30 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="19"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="21"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="20"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="22"/>
+      <c r="A3" s="22"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="24"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:13">
@@ -2216,33 +2219,33 @@
       <c r="M8" s="3"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="19"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="21"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="20"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="22"/>
+      <c r="A10" s="22"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="24"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -2380,33 +2383,33 @@
       <c r="M14" s="3"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="19"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="21"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="20"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="22"/>
+      <c r="A16" s="22"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="24"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -2538,30 +2541,30 @@
       </c>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="19"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="21"/>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="20"/>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="22"/>
+      <c r="A22" s="22"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="24"/>
     </row>
     <row r="23" spans="1:13" ht="28.8">
       <c r="A23" s="13">
@@ -2624,30 +2627,30 @@
       </c>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="19"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="21"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="20"/>
-      <c r="B26" s="21"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="21"/>
-      <c r="J26" s="22"/>
+      <c r="A26" s="22"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="23"/>
+      <c r="I26" s="23"/>
+      <c r="J26" s="24"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="13">

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b1516d80b1b550f1/Documents/GitHub/Command-Line-Interface-Calculator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="378" documentId="11_F25DC773A252ABDACC104830B9DC663C5BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BD51940-C1D9-4B12-A38C-F315D6F9A8CE}"/>
+  <xr:revisionPtr revIDLastSave="381" documentId="11_F25DC773A252ABDACC104830B9DC663C5BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C2415F9-8D1A-4EAB-B258-27323256CFB0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptions" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="176">
   <si>
     <t>Functions</t>
   </si>
@@ -642,7 +642,10 @@
     <t>first_term, ratio, n</t>
   </si>
   <si>
-    <t>Active</t>
+    <t>Finished</t>
+  </si>
+  <si>
+    <t>Shivantha</t>
   </si>
 </sst>
 </file>
@@ -2147,9 +2150,11 @@
       <c r="H6" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="I6" s="4"/>
+      <c r="I6" s="4" t="s">
+        <v>175</v>
+      </c>
       <c r="J6" s="4" t="s">
-        <v>26</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="28.8">

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e253c7f3c843a3b/Documents/GitHub/Command-Line-Interface-Calculator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="374" documentId="11_F25DC773A252ABDACC104830B9DC663C5BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A9D893C-788F-4F13-A4C7-75BB0CE4D469}"/>
+  <xr:revisionPtr revIDLastSave="375" documentId="11_F25DC773A252ABDACC104830B9DC663C5BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AC7FD50-0CAB-48C3-9E1A-27276F778681}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="175">
   <si>
     <t>Functions</t>
   </si>
@@ -640,6 +640,9 @@
   </si>
   <si>
     <t>first_term, ratio, n</t>
+  </si>
+  <si>
+    <t>Anosh</t>
   </si>
 </sst>
 </file>
@@ -2081,7 +2084,9 @@
       <c r="H4" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="I4" s="4"/>
+      <c r="I4" s="4" t="s">
+        <v>174</v>
+      </c>
       <c r="J4" s="4" t="s">
         <v>26</v>
       </c>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b1516d80b1b550f1/Documents/GitHub/Command-Line-Interface-Calculator/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\Command-Line-Interface-Calculator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="381" documentId="11_F25DC773A252ABDACC104830B9DC663C5BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C2415F9-8D1A-4EAB-B258-27323256CFB0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAEB86C8-C66A-4096-BFE8-2D2A57C4B119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptions" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="177">
   <si>
     <t>Functions</t>
   </si>
@@ -646,6 +646,9 @@
   </si>
   <si>
     <t>Shivantha</t>
+  </si>
+  <si>
+    <t>Anosh</t>
   </si>
 </sst>
 </file>
@@ -879,12 +882,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -902,6 +899,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1507,14 +1510,14 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -1617,14 +1620,14 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1">
       <c r="A9" s="2" t="s">
@@ -1707,14 +1710,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1">
       <c r="A14" s="2" t="s">
@@ -1797,14 +1800,14 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
     </row>
     <row r="19" spans="1:6" ht="73.2" customHeight="1">
       <c r="A19" s="2" t="s">
@@ -1847,14 +1850,14 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
     </row>
     <row r="22" spans="1:6" ht="52.2" customHeight="1">
       <c r="A22" s="2" t="s">
@@ -2036,30 +2039,30 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="21"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="19"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="22"/>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="24"/>
+      <c r="A3" s="20"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="22"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:13">
@@ -2182,9 +2185,11 @@
       <c r="H7" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="I7" s="4"/>
+      <c r="I7" s="4" t="s">
+        <v>176</v>
+      </c>
       <c r="J7" s="4" t="s">
-        <v>26</v>
+        <v>174</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
@@ -2224,33 +2229,33 @@
       <c r="M8" s="3"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="21"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="19"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="22"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="23"/>
-      <c r="I10" s="23"/>
-      <c r="J10" s="24"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="22"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -2388,33 +2393,33 @@
       <c r="M14" s="3"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="21"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="19"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="22"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="24"/>
+      <c r="A16" s="20"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="22"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -2546,30 +2551,30 @@
       </c>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="21"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="19"/>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="22"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
-      <c r="J22" s="24"/>
+      <c r="A22" s="20"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="22"/>
     </row>
     <row r="23" spans="1:13" ht="28.8">
       <c r="A23" s="13">
@@ -2632,30 +2637,30 @@
       </c>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="19" t="s">
+      <c r="A25" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="21"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="19"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="22"/>
-      <c r="B26" s="23"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="23"/>
-      <c r="J26" s="24"/>
+      <c r="A26" s="20"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="22"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="13">

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\Command-Line-Interface-Calculator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAEB86C8-C66A-4096-BFE8-2D2A57C4B119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC0D1A41-0301-4F0E-9D98-FB91FF34E596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptions" sheetId="1" r:id="rId1"/>
@@ -1596,7 +1596,7 @@
         <v>44</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>29</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="48" customHeight="1">

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e253c7f3c843a3b/Documents/GitHub/Command-Line-Interface-Calculator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="375" documentId="11_F25DC773A252ABDACC104830B9DC663C5BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AC7FD50-0CAB-48C3-9E1A-27276F778681}"/>
+  <xr:revisionPtr revIDLastSave="376" documentId="11_F25DC773A252ABDACC104830B9DC663C5BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BF70EE2-4E9E-4C70-AD8B-A074CD61E750}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptions" sheetId="1" r:id="rId1"/>
     <sheet name="Parameters" sheetId="2" r:id="rId2"/>
+    <sheet name="Main.py" sheetId="6" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="218">
   <si>
     <t>Functions</t>
   </si>
@@ -643,6 +644,135 @@
   </si>
   <si>
     <t>Anosh</t>
+  </si>
+  <si>
+    <t>Shivantha</t>
+  </si>
+  <si>
+    <t>Nethusha</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Task</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>Main menu</t>
+  </si>
+  <si>
+    <t>Thisew</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>Category navigation</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>Basic menu</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>Area menu</t>
+  </si>
+  <si>
+    <t>M5</t>
+  </si>
+  <si>
+    <t>Volume menu</t>
+  </si>
+  <si>
+    <t>M6</t>
+  </si>
+  <si>
+    <t>Sequence menu</t>
+  </si>
+  <si>
+    <t>M7</t>
+  </si>
+  <si>
+    <t>Physics menu</t>
+  </si>
+  <si>
+    <t>M8</t>
+  </si>
+  <si>
+    <t>User input</t>
+  </si>
+  <si>
+    <t>Kishani</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>Input validation</t>
+  </si>
+  <si>
+    <t>M10</t>
+  </si>
+  <si>
+    <t>Error handling</t>
+  </si>
+  <si>
+    <t>M11</t>
+  </si>
+  <si>
+    <t>Function calls</t>
+  </si>
+  <si>
+    <t>M12</t>
+  </si>
+  <si>
+    <t>Result display</t>
+  </si>
+  <si>
+    <t>M13</t>
+  </si>
+  <si>
+    <t>M14</t>
+  </si>
+  <si>
+    <t>Exit</t>
+  </si>
+  <si>
+    <t>M15</t>
+  </si>
+  <si>
+    <t>Integration testing</t>
+  </si>
+  <si>
+    <t>Both</t>
+  </si>
+  <si>
+    <t>M16</t>
+  </si>
+  <si>
+    <t>Integration debugging</t>
+  </si>
+  <si>
+    <t>M17</t>
+  </si>
+  <si>
+    <t>Final testing &amp; documentation</t>
+  </si>
+  <si>
+    <t>Back/Continue</t>
+  </si>
+  <si>
+    <t>Main loop</t>
+  </si>
+  <si>
+    <t>M18</t>
   </si>
 </sst>
 </file>
@@ -677,7 +807,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -714,8 +844,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -826,11 +968,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -900,11 +1055,43 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="34">
+  <dxfs count="36">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1902,75 +2089,75 @@
     <mergeCell ref="A21:F21"/>
   </mergeCells>
   <conditionalFormatting sqref="F3:F7">
-    <cfRule type="cellIs" dxfId="33" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="5" operator="equal">
       <formula>"Active"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="32" priority="15" operator="containsText" text="Un Finished">
+    <cfRule type="containsText" dxfId="34" priority="15" operator="containsText" text="Un Finished">
       <formula>NOT(ISERROR(SEARCH("Un Finished",F3)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="16" operator="equal">
       <formula>"Un Finished"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="17" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="18" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="19" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="27" priority="20" operator="containsText" text="Un Finished">
+    <cfRule type="containsText" dxfId="29" priority="20" operator="containsText" text="Un Finished">
       <formula>NOT(ISERROR(SEARCH("Un Finished",F3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="21" operator="containsText" text="Un Finished">
+    <cfRule type="containsText" dxfId="28" priority="21" operator="containsText" text="Un Finished">
       <formula>NOT(ISERROR(SEARCH("Un Finished",F3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:F12">
-    <cfRule type="cellIs" dxfId="25" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="4" operator="equal">
       <formula>"Active"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="12" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="13" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="14" operator="equal">
       <formula>"Un Finished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14:F17">
-    <cfRule type="cellIs" dxfId="21" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="3" operator="equal">
       <formula>"Active"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="10" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="11" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19:F20">
-    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="2" operator="equal">
       <formula>"Active"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="8" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="9" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F22:F23">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
       <formula>"Active"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="6" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="7" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2117,7 +2304,9 @@
       <c r="H5" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="I5" s="4"/>
+      <c r="I5" s="4" t="s">
+        <v>174</v>
+      </c>
       <c r="J5" s="4" t="s">
         <v>26</v>
       </c>
@@ -2149,7 +2338,9 @@
       <c r="H6" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="I6" s="4"/>
+      <c r="I6" s="4" t="s">
+        <v>175</v>
+      </c>
       <c r="J6" s="4" t="s">
         <v>26</v>
       </c>
@@ -2179,7 +2370,9 @@
       <c r="H7" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="I7" s="4"/>
+      <c r="I7" s="4" t="s">
+        <v>175</v>
+      </c>
       <c r="J7" s="4" t="s">
         <v>26</v>
       </c>
@@ -2212,7 +2405,9 @@
       <c r="H8" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="I8" s="10"/>
+      <c r="I8" s="10" t="s">
+        <v>176</v>
+      </c>
       <c r="J8" s="4" t="s">
         <v>26</v>
       </c>
@@ -2277,7 +2472,9 @@
       <c r="H11" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="I11" s="11"/>
+      <c r="I11" s="11" t="s">
+        <v>176</v>
+      </c>
       <c r="J11" s="11" t="s">
         <v>26</v>
       </c>
@@ -2310,7 +2507,9 @@
       <c r="H12" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="I12" s="4"/>
+      <c r="I12" s="4" t="s">
+        <v>174</v>
+      </c>
       <c r="J12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2343,7 +2542,9 @@
       <c r="H13" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="I13" s="4"/>
+      <c r="I13" s="4" t="s">
+        <v>174</v>
+      </c>
       <c r="J13" s="11" t="s">
         <v>26</v>
       </c>
@@ -2376,7 +2577,9 @@
       <c r="H14" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="I14" s="4"/>
+      <c r="I14" s="4" t="s">
+        <v>175</v>
+      </c>
       <c r="J14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2441,7 +2644,9 @@
       <c r="H17" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="I17" s="6"/>
+      <c r="I17" s="6" t="s">
+        <v>175</v>
+      </c>
       <c r="J17" s="4" t="s">
         <v>26</v>
       </c>
@@ -2474,7 +2679,9 @@
       <c r="H18" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="I18" s="6"/>
+      <c r="I18" s="6" t="s">
+        <v>176</v>
+      </c>
       <c r="J18" s="4" t="s">
         <v>26</v>
       </c>
@@ -2507,7 +2714,9 @@
       <c r="H19" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="I19" s="6"/>
+      <c r="I19" s="6" t="s">
+        <v>176</v>
+      </c>
       <c r="J19" s="4" t="s">
         <v>26</v>
       </c>
@@ -2537,7 +2746,9 @@
       <c r="H20" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="I20" s="6"/>
+      <c r="I20" s="6" t="s">
+        <v>174</v>
+      </c>
       <c r="J20" s="4" t="s">
         <v>26</v>
       </c>
@@ -2593,7 +2804,9 @@
       <c r="H23" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="I23" s="6"/>
+      <c r="I23" s="6" t="s">
+        <v>174</v>
+      </c>
       <c r="J23" s="4" t="s">
         <v>26</v>
       </c>
@@ -2623,7 +2836,9 @@
       <c r="H24" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="I24" s="6"/>
+      <c r="I24" s="6" t="s">
+        <v>175</v>
+      </c>
       <c r="J24" s="4" t="s">
         <v>26</v>
       </c>
@@ -2679,7 +2894,9 @@
       <c r="H27" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="I27" s="6"/>
+      <c r="I27" s="6" t="s">
+        <v>175</v>
+      </c>
       <c r="J27" s="4" t="s">
         <v>26</v>
       </c>
@@ -2709,7 +2926,9 @@
       <c r="H28" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="I28" s="6"/>
+      <c r="I28" s="6" t="s">
+        <v>176</v>
+      </c>
       <c r="J28" s="4" t="s">
         <v>26</v>
       </c>
@@ -2724,34 +2943,34 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="J4:J8 J11:J14 J17:J20 J23:J24 J27:J28">
-    <cfRule type="cellIs" dxfId="12" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="12" operator="equal">
       <formula>"Unfinished"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="13" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="14" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:J8">
-    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="10" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
       <formula>"Unfinished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11:J14">
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="8" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
       <formula>"Unfinished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J17:J20 J23:J24 J27:J28">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
       <formula>"Unfinished"</formula>
     </cfRule>
     <cfRule type="iconSet" priority="7">
@@ -2763,25 +2982,25 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J17:J20 J27:J28">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J17:J20">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J23:J24">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J27:J28">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2792,4 +3011,299 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3F50124-89B3-4F80-8C5D-4D7BBD731A53}">
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="28.8">
+      <c r="A1" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>189</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>191</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>198</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="C12" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>215</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>216</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>210</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="26" t="s">
+        <v>211</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>210</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="28.8">
+      <c r="A18" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>210</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="28.8">
+      <c r="A19" s="26" t="s">
+        <v>217</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>214</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>210</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2:D19">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"Finished"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>"Unfinished"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D19" xr:uid="{DA1D75CD-0F09-4386-AEE3-1674B1F11DBA}">
+      <formula1>"Unfinished , Finished"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e253c7f3c843a3b/Documents/GitHub/Command-Line-Interface-Calculator/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2b07aacc79a2cf58/Documents/GitHub/Command-Line-Interface-Calculator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="376" documentId="11_F25DC773A252ABDACC104830B9DC663C5BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BF70EE2-4E9E-4C70-AD8B-A074CD61E750}"/>
+  <xr:revisionPtr revIDLastSave="382" documentId="11_F25DC773A252ABDACC104830B9DC663C5BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5DBABF1-EA74-4149-A7B5-9C1402458688}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptions" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="220">
   <si>
     <t>Functions</t>
   </si>
@@ -773,6 +773,12 @@
   </si>
   <si>
     <t>M18</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Finished</t>
   </si>
 </sst>
 </file>
@@ -1031,6 +1037,21 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1048,21 +1069,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1691,14 +1697,14 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -1717,7 +1723,7 @@
         <v>31</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="42" customHeight="1">
@@ -1801,14 +1807,14 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="24"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1">
       <c r="A9" s="2" t="s">
@@ -1891,14 +1897,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1">
       <c r="A14" s="2" t="s">
@@ -1981,14 +1987,14 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
     </row>
     <row r="19" spans="1:6" ht="73.2" customHeight="1">
       <c r="A19" s="2" t="s">
@@ -2031,14 +2037,14 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
-      <c r="A21" s="24" t="s">
+      <c r="A21" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
     </row>
     <row r="22" spans="1:6" ht="52.2" customHeight="1">
       <c r="A22" s="2" t="s">
@@ -2220,30 +2226,30 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="19"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="24"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="20"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="22"/>
+      <c r="A3" s="25"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="27"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:13">
@@ -2342,7 +2348,7 @@
         <v>175</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="28.8">
@@ -2374,7 +2380,7 @@
         <v>175</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
@@ -2416,33 +2422,33 @@
       <c r="M8" s="3"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="19"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="24"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="20"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="22"/>
+      <c r="A10" s="25"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="27"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -2588,33 +2594,33 @@
       <c r="M14" s="3"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="19"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="24"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="20"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="22"/>
+      <c r="A16" s="25"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="27"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -2754,30 +2760,30 @@
       </c>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="19"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="24"/>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="20"/>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="22"/>
+      <c r="A22" s="25"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="26"/>
+      <c r="J22" s="27"/>
     </row>
     <row r="23" spans="1:13" ht="28.8">
       <c r="A23" s="13">
@@ -2844,30 +2850,30 @@
       </c>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="19"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="24"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="20"/>
-      <c r="B26" s="21"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="21"/>
-      <c r="J26" s="22"/>
+      <c r="A26" s="25"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="27"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="13">
@@ -3024,7 +3030,7 @@
     <col min="4" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.8">
+    <row r="1" spans="1:4">
       <c r="A1" s="7" t="s">
         <v>177</v>
       </c>
@@ -3034,259 +3040,259 @@
       <c r="C1" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="17" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="19" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="19" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="19" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="19" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="19" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="19" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="19" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="19" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="19" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="18" t="s">
         <v>200</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D11" s="19" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="B12" s="26" t="s">
+      <c r="B12" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="D12" s="27" t="s">
+      <c r="D12" s="19" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="D13" s="27" t="s">
+      <c r="D13" s="19" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="B14" s="26" t="s">
+      <c r="B14" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="D14" s="27" t="s">
+      <c r="D14" s="19" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="26" t="s">
+      <c r="A15" s="18" t="s">
         <v>206</v>
       </c>
-      <c r="B15" s="26" t="s">
+      <c r="B15" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="D15" s="19" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="18" t="s">
         <v>216</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="D16" s="27" t="s">
+      <c r="D16" s="19" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="19" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="28.8">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="B18" s="26" t="s">
+      <c r="B18" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="19" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28.8">
-      <c r="A19" s="26" t="s">
+      <c r="A19" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="C19" s="26" t="s">
+      <c r="C19" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="D19" s="19" t="s">
         <v>26</v>
       </c>
     </row>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e253c7f3c843a3b/Documents/GitHub/Command-Line-Interface-Calculator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="376" documentId="11_F25DC773A252ABDACC104830B9DC663C5BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BF70EE2-4E9E-4C70-AD8B-A074CD61E750}"/>
+  <xr:revisionPtr revIDLastSave="390" documentId="11_F25DC773A252ABDACC104830B9DC663C5BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1E73930-2845-4089-B920-0201DDF35381}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptions" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="220">
   <si>
     <t>Functions</t>
   </si>
@@ -751,9 +751,6 @@
     <t>Integration testing</t>
   </si>
   <si>
-    <t>Both</t>
-  </si>
-  <si>
     <t>M16</t>
   </si>
   <si>
@@ -773,6 +770,15 @@
   </si>
   <si>
     <t>M18</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Finished</t>
+  </si>
+  <si>
+    <t>ALL</t>
   </si>
 </sst>
 </file>
@@ -1031,6 +1037,15 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1054,15 +1069,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1691,14 +1697,14 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -1717,7 +1723,7 @@
         <v>31</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>29</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="42" customHeight="1">
@@ -1801,14 +1807,14 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="24"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1">
       <c r="A9" s="2" t="s">
@@ -1891,14 +1897,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1">
       <c r="A14" s="2" t="s">
@@ -1981,14 +1987,14 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
     </row>
     <row r="19" spans="1:6" ht="73.2" customHeight="1">
       <c r="A19" s="2" t="s">
@@ -2031,14 +2037,14 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
-      <c r="A21" s="24" t="s">
+      <c r="A21" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
     </row>
     <row r="22" spans="1:6" ht="52.2" customHeight="1">
       <c r="A22" s="2" t="s">
@@ -2220,30 +2226,30 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="19"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="22"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="20"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="22"/>
+      <c r="A3" s="23"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="25"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:13">
@@ -2342,7 +2348,7 @@
         <v>175</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>26</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="28.8">
@@ -2374,7 +2380,7 @@
         <v>175</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>26</v>
+        <v>218</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
@@ -2416,33 +2422,33 @@
       <c r="M8" s="3"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="19"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="22"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="20"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="22"/>
+      <c r="A10" s="23"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="25"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -2588,33 +2594,33 @@
       <c r="M14" s="3"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="19"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="22"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="20"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="22"/>
+      <c r="A16" s="23"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="25"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -2754,30 +2760,30 @@
       </c>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="19"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="22"/>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="20"/>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="22"/>
+      <c r="A22" s="23"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="25"/>
     </row>
     <row r="23" spans="1:13" ht="28.8">
       <c r="A23" s="13">
@@ -2844,30 +2850,30 @@
       </c>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="19"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="22"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="20"/>
-      <c r="B26" s="21"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="21"/>
-      <c r="J26" s="22"/>
+      <c r="A26" s="23"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="25"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="13">
@@ -3024,7 +3030,7 @@
     <col min="4" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.8">
+    <row r="1" spans="1:4">
       <c r="A1" s="7" t="s">
         <v>177</v>
       </c>
@@ -3034,259 +3040,259 @@
       <c r="C1" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="17" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="19" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="19" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="C6" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="D4" s="27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="26" t="s">
-        <v>186</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>187</v>
-      </c>
-      <c r="C5" s="26" t="s">
+      <c r="D6" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="C9" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="D5" s="27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="26" t="s">
-        <v>188</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>189</v>
-      </c>
-      <c r="C6" s="26" t="s">
+      <c r="D9" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="C12" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="D6" s="27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>191</v>
-      </c>
-      <c r="C7" s="26" t="s">
+      <c r="D12" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="C15" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="D7" s="27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>181</v>
-      </c>
-      <c r="D8" s="27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>195</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>181</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>200</v>
-      </c>
-      <c r="C11" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="D11" s="27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="26" t="s">
-        <v>201</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>181</v>
-      </c>
-      <c r="D12" s="27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="B13" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="C13" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="D13" s="27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="B14" s="26" t="s">
+      <c r="D15" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B16" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="C14" s="26" t="s">
-        <v>181</v>
-      </c>
-      <c r="D14" s="27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="B15" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="C15" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="D15" s="27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="26" t="s">
-        <v>208</v>
-      </c>
-      <c r="B16" s="26" t="s">
+      <c r="C16" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="28.8">
+      <c r="A18" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="28.8">
+      <c r="A19" s="18" t="s">
         <v>216</v>
       </c>
-      <c r="C16" s="26" t="s">
-        <v>210</v>
-      </c>
-      <c r="D16" s="27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="26" t="s">
-        <v>211</v>
-      </c>
-      <c r="B17" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="C17" s="26" t="s">
-        <v>210</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="28.8">
-      <c r="A18" s="26" t="s">
+      <c r="B19" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="B18" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>210</v>
-      </c>
-      <c r="D18" s="27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="28.8">
-      <c r="A19" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="B19" s="26" t="s">
-        <v>214</v>
-      </c>
-      <c r="C19" s="26" t="s">
-        <v>210</v>
-      </c>
-      <c r="D19" s="27" t="s">
+      <c r="C19" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="D19" s="19" t="s">
         <v>26</v>
       </c>
     </row>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e253c7f3c843a3b/Documents/GitHub/Command-Line-Interface-Calculator/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\Command-Line-Interface-Calculator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="390" documentId="11_F25DC773A252ABDACC104830B9DC663C5BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1E73930-2845-4089-B920-0201DDF35381}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E01E32-478F-4EBB-B3BE-D45894FF2BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="9960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptions" sheetId="1" r:id="rId1"/>
@@ -1046,6 +1046,12 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1063,12 +1069,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1697,14 +1697,14 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -1807,14 +1807,14 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1">
       <c r="A9" s="2" t="s">
@@ -1897,14 +1897,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1">
       <c r="A14" s="2" t="s">
@@ -1987,14 +1987,14 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="27"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
     </row>
     <row r="19" spans="1:6" ht="73.2" customHeight="1">
       <c r="A19" s="2" t="s">
@@ -2037,14 +2037,14 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
-      <c r="A21" s="27" t="s">
+      <c r="A21" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
     </row>
     <row r="22" spans="1:6" ht="52.2" customHeight="1">
       <c r="A22" s="2" t="s">
@@ -2226,30 +2226,30 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="22"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="24"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="23"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="25"/>
+      <c r="A3" s="25"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="27"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:13">
@@ -2281,7 +2281,7 @@
         <v>174</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>26</v>
+        <v>218</v>
       </c>
       <c r="L4" s="3"/>
     </row>
@@ -2314,7 +2314,7 @@
         <v>174</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>26</v>
+        <v>218</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
@@ -2422,33 +2422,33 @@
       <c r="M8" s="3"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="22"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="24"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="23"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="25"/>
+      <c r="A10" s="25"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="27"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -2517,7 +2517,7 @@
         <v>174</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>26</v>
+        <v>218</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
@@ -2552,7 +2552,7 @@
         <v>174</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>26</v>
+        <v>218</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
@@ -2594,33 +2594,33 @@
       <c r="M14" s="3"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="22"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="24"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="23"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="25"/>
+      <c r="A16" s="25"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="27"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -2756,34 +2756,34 @@
         <v>174</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>26</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="22"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="24"/>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="23"/>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="25"/>
+      <c r="A22" s="25"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="26"/>
+      <c r="J22" s="27"/>
     </row>
     <row r="23" spans="1:13" ht="28.8">
       <c r="A23" s="13">
@@ -2814,7 +2814,7 @@
         <v>174</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>26</v>
+        <v>218</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="26.4">
@@ -2850,30 +2850,30 @@
       </c>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="21"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="21"/>
-      <c r="J25" s="22"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="24"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="23"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="24"/>
-      <c r="J26" s="25"/>
+      <c r="A26" s="25"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="27"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="13">

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\Command-Line-Interface-Calculator\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e253c7f3c843a3b/Documents/GitHub/Command-Line-Interface-Calculator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E01E32-478F-4EBB-B3BE-D45894FF2BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{41E01E32-478F-4EBB-B3BE-D45894FF2BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09A740AA-4F4D-4517-93C2-5A8EFD72921A}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="9960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptions" sheetId="1" r:id="rId1"/>
@@ -1046,12 +1046,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1069,6 +1063,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1697,14 +1697,14 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -1807,14 +1807,14 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1">
       <c r="A9" s="2" t="s">
@@ -1897,14 +1897,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1">
       <c r="A14" s="2" t="s">
@@ -1987,14 +1987,14 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
     </row>
     <row r="19" spans="1:6" ht="73.2" customHeight="1">
       <c r="A19" s="2" t="s">
@@ -2037,14 +2037,14 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
     </row>
     <row r="22" spans="1:6" ht="52.2" customHeight="1">
       <c r="A22" s="2" t="s">
@@ -2226,30 +2226,30 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="24"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="22"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="25"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="27"/>
+      <c r="A3" s="23"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="25"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:13">
@@ -2422,33 +2422,33 @@
       <c r="M8" s="3"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="24"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="22"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="25"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="27"/>
+      <c r="A10" s="23"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="25"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -2594,33 +2594,33 @@
       <c r="M14" s="3"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="24"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="22"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="27"/>
+      <c r="A16" s="23"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="25"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -2760,30 +2760,30 @@
       </c>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="B21" s="23"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="24"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="22"/>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="25"/>
-      <c r="B22" s="26"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="27"/>
+      <c r="A22" s="23"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="25"/>
     </row>
     <row r="23" spans="1:13" ht="28.8">
       <c r="A23" s="13">
@@ -2850,30 +2850,30 @@
       </c>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="24"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="22"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="25"/>
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="27"/>
+      <c r="A26" s="23"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="25"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="13">
@@ -3080,10 +3080,10 @@
         <v>185</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>26</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3094,7 +3094,7 @@
         <v>187</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>26</v>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e253c7f3c843a3b/Documents/GitHub/Command-Line-Interface-Calculator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{41E01E32-478F-4EBB-B3BE-D45894FF2BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09A740AA-4F4D-4517-93C2-5A8EFD72921A}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{41E01E32-478F-4EBB-B3BE-D45894FF2BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60B925A1-C841-459A-AEE9-730C350F7FFE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="210">
   <si>
     <t>Functions</t>
   </si>
@@ -706,60 +706,33 @@
     <t>M8</t>
   </si>
   <si>
-    <t>User input</t>
-  </si>
-  <si>
     <t>Kishani</t>
   </si>
   <si>
     <t>M9</t>
   </si>
   <si>
-    <t>Input validation</t>
-  </si>
-  <si>
     <t>M10</t>
   </si>
   <si>
-    <t>Error handling</t>
-  </si>
-  <si>
     <t>M11</t>
   </si>
   <si>
-    <t>Function calls</t>
-  </si>
-  <si>
     <t>M12</t>
   </si>
   <si>
-    <t>Result display</t>
-  </si>
-  <si>
     <t>M13</t>
   </si>
   <si>
-    <t>M14</t>
-  </si>
-  <si>
     <t>Exit</t>
   </si>
   <si>
-    <t>M15</t>
-  </si>
-  <si>
     <t>Integration testing</t>
   </si>
   <si>
-    <t>M16</t>
-  </si>
-  <si>
     <t>Integration debugging</t>
   </si>
   <si>
-    <t>M17</t>
-  </si>
-  <si>
     <t>Final testing &amp; documentation</t>
   </si>
   <si>
@@ -767,9 +740,6 @@
   </si>
   <si>
     <t>Main loop</t>
-  </si>
-  <si>
-    <t>M18</t>
   </si>
   <si>
     <t>Active</t>
@@ -1046,6 +1016,12 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1063,12 +1039,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1697,14 +1667,14 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -1723,7 +1693,7 @@
         <v>31</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="42" customHeight="1">
@@ -1807,14 +1777,14 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1">
       <c r="A9" s="2" t="s">
@@ -1897,14 +1867,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1">
       <c r="A14" s="2" t="s">
@@ -1987,14 +1957,14 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="27"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
     </row>
     <row r="19" spans="1:6" ht="73.2" customHeight="1">
       <c r="A19" s="2" t="s">
@@ -2037,14 +2007,14 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
-      <c r="A21" s="27" t="s">
+      <c r="A21" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
     </row>
     <row r="22" spans="1:6" ht="52.2" customHeight="1">
       <c r="A22" s="2" t="s">
@@ -2226,30 +2196,30 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="22"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="24"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="23"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="25"/>
+      <c r="A3" s="25"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="27"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:13">
@@ -2281,7 +2251,7 @@
         <v>174</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="L4" s="3"/>
     </row>
@@ -2314,7 +2284,7 @@
         <v>174</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
@@ -2348,7 +2318,7 @@
         <v>175</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="28.8">
@@ -2380,7 +2350,7 @@
         <v>175</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
@@ -2422,33 +2392,33 @@
       <c r="M8" s="3"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="22"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="24"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="23"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="25"/>
+      <c r="A10" s="25"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="27"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -2517,7 +2487,7 @@
         <v>174</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
@@ -2552,7 +2522,7 @@
         <v>174</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
@@ -2594,33 +2564,33 @@
       <c r="M14" s="3"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="22"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="24"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="23"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="25"/>
+      <c r="A16" s="25"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="27"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -2756,34 +2726,34 @@
         <v>174</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="22"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="24"/>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="23"/>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="25"/>
+      <c r="A22" s="25"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="26"/>
+      <c r="J22" s="27"/>
     </row>
     <row r="23" spans="1:13" ht="28.8">
       <c r="A23" s="13">
@@ -2814,7 +2784,7 @@
         <v>174</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="26.4">
@@ -2850,30 +2820,30 @@
       </c>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="21"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="21"/>
-      <c r="J25" s="22"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="24"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="23"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="24"/>
-      <c r="J26" s="25"/>
+      <c r="A26" s="25"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="27"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="13">
@@ -3021,7 +2991,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3F50124-89B3-4F80-8C5D-4D7BBD731A53}">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -3066,7 +3036,7 @@
         <v>183</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>26</v>
@@ -3080,10 +3050,10 @@
         <v>185</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3147,10 +3117,10 @@
         <v>194</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="D9" s="19" t="s">
         <v>26</v>
@@ -3158,13 +3128,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="18" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>26</v>
@@ -3172,13 +3142,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="18" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="D11" s="19" t="s">
         <v>26</v>
@@ -3186,118 +3156,49 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="18" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B12" s="18" t="s">
         <v>202</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>181</v>
+        <v>209</v>
       </c>
       <c r="D12" s="19" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" ht="28.8">
       <c r="A13" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="B13" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>204</v>
-      </c>
       <c r="C13" s="18" t="s">
-        <v>174</v>
+        <v>209</v>
       </c>
       <c r="D13" s="19" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" ht="28.8">
       <c r="A14" s="18" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>181</v>
+        <v>209</v>
       </c>
       <c r="D14" s="19" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>215</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="28.8">
-      <c r="A18" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>211</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="28.8">
-      <c r="A19" s="18" t="s">
-        <v>216</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>26</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D19">
+  <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="D2:D14">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
@@ -3306,7 +3207,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D19" xr:uid="{DA1D75CD-0F09-4386-AEE3-1674B1F11DBA}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D14" xr:uid="{DA1D75CD-0F09-4386-AEE3-1674B1F11DBA}">
       <formula1>"Unfinished , Finished"</formula1>
     </dataValidation>
   </dataValidations>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e253c7f3c843a3b/Documents/GitHub/Command-Line-Interface-Calculator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{41E01E32-478F-4EBB-B3BE-D45894FF2BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60B925A1-C841-459A-AEE9-730C350F7FFE}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{41E01E32-478F-4EBB-B3BE-D45894FF2BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDB1AB3E-35F2-4780-81A7-7AB0AA68EF86}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptions" sheetId="1" r:id="rId1"/>
@@ -2385,7 +2385,7 @@
         <v>176</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>26</v>
+        <v>208</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
@@ -2659,7 +2659,7 @@
         <v>176</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>26</v>
+        <v>208</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
@@ -2694,7 +2694,7 @@
         <v>176</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>26</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="28.8">
@@ -2986,6 +2986,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\Command-Line-Interface-Calculator\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b1516d80b1b550f1/Documents/GitHub/Command-Line-Interface-Calculator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E01E32-478F-4EBB-B3BE-D45894FF2BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{41E01E32-478F-4EBB-B3BE-D45894FF2BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DDB2152-346C-45DF-8911-EF9EE8133F60}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="9960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptions" sheetId="1" r:id="rId1"/>
@@ -2587,7 +2587,7 @@
         <v>175</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>26</v>
+        <v>218</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
@@ -2654,7 +2654,7 @@
         <v>175</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>26</v>
+        <v>218</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
@@ -2846,7 +2846,7 @@
         <v>175</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>26</v>
+        <v>218</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -2904,7 +2904,7 @@
         <v>175</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>26</v>
+        <v>218</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="28.8">

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b1516d80b1b550f1/Documents/GitHub/Command-Line-Interface-Calculator/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e253c7f3c843a3b/Documents/GitHub/Command-Line-Interface-Calculator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{41E01E32-478F-4EBB-B3BE-D45894FF2BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DDB2152-346C-45DF-8911-EF9EE8133F60}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="121_S{F28FAFD6-B2C6-5E8D-ADE2-951DB646B9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptions" sheetId="1" r:id="rId1"/>
@@ -1046,12 +1046,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1070,6 +1064,12 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1099,6 +1099,157 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1228,157 +1379,6 @@
       <font>
         <color rgb="FFFF0000"/>
       </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1397,6 +1397,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1697,14 +1701,14 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -1807,14 +1811,14 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1">
       <c r="A9" s="2" t="s">
@@ -1897,14 +1901,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1">
       <c r="A14" s="2" t="s">
@@ -1987,14 +1991,14 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
     </row>
     <row r="19" spans="1:6" ht="73.2" customHeight="1">
       <c r="A19" s="2" t="s">
@@ -2037,14 +2041,14 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
     </row>
     <row r="22" spans="1:6" ht="52.2" customHeight="1">
       <c r="A22" s="2" t="s">
@@ -2095,75 +2099,75 @@
     <mergeCell ref="A21:F21"/>
   </mergeCells>
   <conditionalFormatting sqref="F3:F7">
-    <cfRule type="cellIs" dxfId="35" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="5" operator="equal">
       <formula>"Active"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="15" operator="containsText" text="Un Finished">
+    <cfRule type="containsText" dxfId="21" priority="15" operator="containsText" text="Un Finished">
       <formula>NOT(ISERROR(SEARCH("Un Finished",F3)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="16" operator="equal">
       <formula>"Un Finished"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="17" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="18" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="19" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="29" priority="20" operator="containsText" text="Un Finished">
+    <cfRule type="containsText" dxfId="16" priority="20" operator="containsText" text="Un Finished">
       <formula>NOT(ISERROR(SEARCH("Un Finished",F3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="21" operator="containsText" text="Un Finished">
+    <cfRule type="containsText" dxfId="15" priority="21" operator="containsText" text="Un Finished">
       <formula>NOT(ISERROR(SEARCH("Un Finished",F3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:F12">
-    <cfRule type="cellIs" dxfId="27" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
       <formula>"Active"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="12" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="13" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="14" operator="equal">
       <formula>"Un Finished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14:F17">
-    <cfRule type="cellIs" dxfId="23" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
       <formula>"Active"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19:F20">
-    <cfRule type="cellIs" dxfId="20" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"Active"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="9" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F22:F23">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"Active"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2226,30 +2230,30 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="24"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="22"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="25"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="27"/>
+      <c r="A3" s="23"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="25"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:13">
@@ -2422,33 +2426,33 @@
       <c r="M8" s="3"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="24"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="22"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="25"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="27"/>
+      <c r="A10" s="23"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="25"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -2594,33 +2598,33 @@
       <c r="M14" s="3"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="24"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="22"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="27"/>
+      <c r="A16" s="23"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="25"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -2760,30 +2764,30 @@
       </c>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="B21" s="23"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="24"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="22"/>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="25"/>
-      <c r="B22" s="26"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="27"/>
+      <c r="A22" s="23"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="25"/>
     </row>
     <row r="23" spans="1:13" ht="28.8">
       <c r="A23" s="13">
@@ -2850,30 +2854,30 @@
       </c>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="24"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="22"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="25"/>
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="27"/>
+      <c r="A26" s="23"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="25"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="13">
@@ -2949,34 +2953,34 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="J4:J8 J11:J14 J17:J20 J23:J24 J27:J28">
-    <cfRule type="cellIs" dxfId="14" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="12" operator="equal">
       <formula>"Unfinished"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="13" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="14" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:J8">
-    <cfRule type="cellIs" dxfId="11" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="10" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="11" operator="equal">
       <formula>"Unfinished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11:J14">
-    <cfRule type="cellIs" dxfId="9" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="8" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="9" operator="equal">
       <formula>"Unfinished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J17:J20 J23:J24 J27:J28">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="6" operator="equal">
       <formula>"Unfinished"</formula>
     </cfRule>
     <cfRule type="iconSet" priority="7">
@@ -2988,25 +2992,25 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J17:J20 J27:J28">
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="5" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J17:J20">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="4" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J23:J24">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="3" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J27:J28">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e253c7f3c843a3b/Documents/GitHub/Command-Line-Interface-Calculator/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2b07aacc79a2cf58/Documents/GitHub/Command-Line-Interface-Calculator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="121_S{F28FAFD6-B2C6-5E8D-ADE2-951DB646B9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="121_S{F28FAFD6-B2C6-5E8D-ADE2-951DB646B9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DEC3090-9E34-4A08-B604-1D0641F615B0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptions" sheetId="1" r:id="rId1"/>
@@ -1099,157 +1099,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1379,6 +1228,157 @@
       <font>
         <color rgb="FFFF0000"/>
       </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1397,10 +1397,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1727,7 +1723,7 @@
         <v>31</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="42" customHeight="1">
@@ -1747,7 +1743,7 @@
         <v>35</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="30" customHeight="1">
@@ -1767,7 +1763,7 @@
         <v>40</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="48.6" customHeight="1">
@@ -1787,7 +1783,7 @@
         <v>44</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="48" customHeight="1">
@@ -1807,7 +1803,7 @@
         <v>48</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1">
@@ -1857,7 +1853,7 @@
         <v>56</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1">
@@ -1877,7 +1873,7 @@
         <v>59</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>29</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1">
@@ -1897,7 +1893,7 @@
         <v>64</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1">
@@ -1927,7 +1923,7 @@
         <v>70</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>29</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="30" customHeight="1">
@@ -1987,7 +1983,7 @@
         <v>78</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>29</v>
+        <v>217</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
@@ -2017,7 +2013,7 @@
         <v>82</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>26</v>
+        <v>217</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="78" customHeight="1">
@@ -2037,7 +2033,7 @@
         <v>82</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
@@ -2067,7 +2063,7 @@
         <v>87</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>26</v>
+        <v>217</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="43.8" customHeight="1">
@@ -2099,75 +2095,75 @@
     <mergeCell ref="A21:F21"/>
   </mergeCells>
   <conditionalFormatting sqref="F3:F7">
-    <cfRule type="cellIs" dxfId="22" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="5" operator="equal">
       <formula>"Active"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="15" operator="containsText" text="Un Finished">
+    <cfRule type="containsText" dxfId="34" priority="15" operator="containsText" text="Un Finished">
       <formula>NOT(ISERROR(SEARCH("Un Finished",F3)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="16" operator="equal">
       <formula>"Un Finished"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="17" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="18" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="19" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="20" operator="containsText" text="Un Finished">
+    <cfRule type="containsText" dxfId="29" priority="20" operator="containsText" text="Un Finished">
       <formula>NOT(ISERROR(SEARCH("Un Finished",F3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="21" operator="containsText" text="Un Finished">
+    <cfRule type="containsText" dxfId="28" priority="21" operator="containsText" text="Un Finished">
       <formula>NOT(ISERROR(SEARCH("Un Finished",F3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:F12">
-    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="4" operator="equal">
       <formula>"Active"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="12" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="13" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="14" operator="equal">
       <formula>"Un Finished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14:F17">
-    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="3" operator="equal">
       <formula>"Active"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="10" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="11" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19:F20">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="2" operator="equal">
       <formula>"Active"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="8" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="9" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F22:F23">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
       <formula>"Active"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="6" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="7" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2953,34 +2949,34 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="J4:J8 J11:J14 J17:J20 J23:J24 J27:J28">
-    <cfRule type="cellIs" dxfId="35" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="12" operator="equal">
       <formula>"Unfinished"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="13" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="14" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:J8">
-    <cfRule type="cellIs" dxfId="32" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="10" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
       <formula>"Unfinished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11:J14">
-    <cfRule type="cellIs" dxfId="30" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="8" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
       <formula>"Unfinished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J17:J20 J23:J24 J27:J28">
-    <cfRule type="cellIs" dxfId="28" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
       <formula>"Unfinished"</formula>
     </cfRule>
     <cfRule type="iconSet" priority="7">
@@ -2992,25 +2988,25 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J17:J20 J27:J28">
-    <cfRule type="cellIs" dxfId="27" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J17:J20">
-    <cfRule type="cellIs" dxfId="26" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J23:J24">
-    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J27:J28">
-    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"Finished"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2b07aacc79a2cf58/Documents/GitHub/Command-Line-Interface-Calculator/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e253c7f3c843a3b/Documents/GitHub/Command-Line-Interface-Calculator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="121_S{F28FAFD6-B2C6-5E8D-ADE2-951DB646B9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DEC3090-9E34-4A08-B604-1D0641F615B0}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="121_S{F28FAFD6-B2C6-5E8D-ADE2-951DB646B9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60CAFC0A-B116-4256-A717-DB137F490661}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptions" sheetId="1" r:id="rId1"/>
@@ -1046,6 +1046,12 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1063,12 +1069,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1697,14 +1697,14 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -1807,14 +1807,14 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1">
       <c r="A9" s="2" t="s">
@@ -1833,7 +1833,7 @@
         <v>51</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>29</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1">
@@ -1873,7 +1873,7 @@
         <v>59</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1">
@@ -1897,14 +1897,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1">
       <c r="A14" s="2" t="s">
@@ -1987,14 +1987,14 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="27"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
     </row>
     <row r="19" spans="1:6" ht="73.2" customHeight="1">
       <c r="A19" s="2" t="s">
@@ -2037,14 +2037,14 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
-      <c r="A21" s="27" t="s">
+      <c r="A21" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
     </row>
     <row r="22" spans="1:6" ht="52.2" customHeight="1">
       <c r="A22" s="2" t="s">
@@ -2226,30 +2226,30 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="22"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="24"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="23"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="25"/>
+      <c r="A3" s="25"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="27"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:13">
@@ -2422,33 +2422,33 @@
       <c r="M8" s="3"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="22"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="24"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="23"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="25"/>
+      <c r="A10" s="25"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="27"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -2482,7 +2482,7 @@
         <v>176</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>26</v>
+        <v>218</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
@@ -2594,33 +2594,33 @@
       <c r="M14" s="3"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="22"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="24"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="23"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="25"/>
+      <c r="A16" s="25"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="27"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -2760,30 +2760,30 @@
       </c>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="22"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="24"/>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="23"/>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="25"/>
+      <c r="A22" s="25"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="26"/>
+      <c r="J22" s="27"/>
     </row>
     <row r="23" spans="1:13" ht="28.8">
       <c r="A23" s="13">
@@ -2850,30 +2850,30 @@
       </c>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="21"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="21"/>
-      <c r="J25" s="22"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="24"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="23"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="24"/>
-      <c r="J26" s="25"/>
+      <c r="A26" s="25"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="27"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="13">

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e253c7f3c843a3b/Documents/GitHub/Command-Line-Interface-Calculator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="121_S{F28FAFD6-B2C6-5E8D-ADE2-951DB646B9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60CAFC0A-B116-4256-A717-DB137F490661}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="121_S{F28FAFD6-B2C6-5E8D-ADE2-951DB646B9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90E38DE8-F30A-4BDA-8905-B4A42BBDF022}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2013,7 +2013,7 @@
         <v>82</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="78" customHeight="1">
@@ -2063,7 +2063,7 @@
         <v>87</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="43.8" customHeight="1">

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e253c7f3c843a3b/Documents/GitHub/Command-Line-Interface-Calculator/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2b07aacc79a2cf58/Documents/GitHub/Command-Line-Interface-Calculator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="121_S{F28FAFD6-B2C6-5E8D-ADE2-951DB646B9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90E38DE8-F30A-4BDA-8905-B4A42BBDF022}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="121_S{F28FAFD6-B2C6-5E8D-ADE2-951DB646B9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19642A54-5B8F-41A2-8BD4-2E6113E1639C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptions" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="219">
   <si>
     <t>Functions</t>
   </si>
@@ -770,9 +770,6 @@
   </si>
   <si>
     <t>M18</t>
-  </si>
-  <si>
-    <t>Active</t>
   </si>
   <si>
     <t>Finished</t>
@@ -1723,7 +1720,7 @@
         <v>31</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="42" customHeight="1">
@@ -1743,7 +1740,7 @@
         <v>35</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="30" customHeight="1">
@@ -1763,7 +1760,7 @@
         <v>40</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="48.6" customHeight="1">
@@ -1783,7 +1780,7 @@
         <v>44</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="48" customHeight="1">
@@ -1803,7 +1800,7 @@
         <v>48</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1">
@@ -1833,7 +1830,7 @@
         <v>51</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1">
@@ -1853,7 +1850,7 @@
         <v>56</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1">
@@ -1873,7 +1870,7 @@
         <v>59</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1">
@@ -1893,7 +1890,7 @@
         <v>64</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1">
@@ -2013,7 +2010,7 @@
         <v>82</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="78" customHeight="1">
@@ -2033,7 +2030,7 @@
         <v>82</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
@@ -2063,7 +2060,7 @@
         <v>87</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="43.8" customHeight="1">
@@ -2281,7 +2278,7 @@
         <v>174</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="L4" s="3"/>
     </row>
@@ -2314,7 +2311,7 @@
         <v>174</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
@@ -2348,7 +2345,7 @@
         <v>175</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="28.8">
@@ -2380,7 +2377,7 @@
         <v>175</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
@@ -2482,7 +2479,7 @@
         <v>176</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
@@ -2517,7 +2514,7 @@
         <v>174</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
@@ -2552,7 +2549,7 @@
         <v>174</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
@@ -2587,7 +2584,7 @@
         <v>175</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
@@ -2654,7 +2651,7 @@
         <v>175</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
@@ -2756,7 +2753,7 @@
         <v>174</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -2814,7 +2811,7 @@
         <v>174</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="26.4">
@@ -2846,7 +2843,7 @@
         <v>175</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -2904,7 +2901,7 @@
         <v>175</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="28.8">
@@ -3248,7 +3245,7 @@
         <v>215</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D16" s="19" t="s">
         <v>26</v>
@@ -3262,7 +3259,7 @@
         <v>209</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D17" s="19" t="s">
         <v>26</v>
@@ -3276,7 +3273,7 @@
         <v>211</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D18" s="19" t="s">
         <v>26</v>
@@ -3290,7 +3287,7 @@
         <v>213</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D19" s="19" t="s">
         <v>26</v>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2b07aacc79a2cf58/Documents/GitHub/Command-Line-Interface-Calculator/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e253c7f3c843a3b/Documents/GitHub/Command-Line-Interface-Calculator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="121_S{F28FAFD6-B2C6-5E8D-ADE2-951DB646B9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19642A54-5B8F-41A2-8BD4-2E6113E1639C}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="121_S{F28FAFD6-B2C6-5E8D-ADE2-951DB646B9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4814E68-30D3-4E9C-A6CB-644349CD7101}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptions" sheetId="1" r:id="rId1"/>
@@ -2412,7 +2412,7 @@
         <v>176</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>26</v>
+        <v>217</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>

--- a/jobs.xlsx
+++ b/jobs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e253c7f3c843a3b/Documents/GitHub/Command-Line-Interface-Calculator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="121_S{F28FAFD6-B2C6-5E8D-ADE2-951DB646B9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4814E68-30D3-4E9C-A6CB-644349CD7101}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="121_S{F28FAFD6-B2C6-5E8D-ADE2-951DB646B9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E926D14E-877C-430F-8AB2-6D2BEA19648B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptions" sheetId="1" r:id="rId1"/>
@@ -1043,12 +1043,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1066,6 +1060,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1694,14 +1694,14 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
     </row>
     <row r="3" spans="1:6" ht="30" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -1804,14 +1804,14 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1">
       <c r="A9" s="2" t="s">
@@ -1894,14 +1894,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1">
       <c r="A14" s="2" t="s">
@@ -1940,7 +1940,7 @@
         <v>71</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>29</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="30" customHeight="1">
@@ -1960,7 +1960,7 @@
         <v>74</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>29</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1">
@@ -1984,14 +1984,14 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
     </row>
     <row r="19" spans="1:6" ht="73.2" customHeight="1">
       <c r="A19" s="2" t="s">
@@ -2034,14 +2034,14 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
     </row>
     <row r="22" spans="1:6" ht="52.2" customHeight="1">
       <c r="A22" s="2" t="s">
@@ -2223,30 +2223,30 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="24"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="22"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="25"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="27"/>
+      <c r="A3" s="23"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="25"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:13">
@@ -2419,33 +2419,33 @@
       <c r="M8" s="3"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="24"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="22"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="25"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="27"/>
+      <c r="A10" s="23"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="25"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -2591,33 +2591,33 @@
       <c r="M14" s="3"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="24"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="22"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="27"/>
+      <c r="A16" s="23"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="25"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -2686,7 +2686,7 @@
         <v>176</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>26</v>
+        <v>217</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
@@ -2721,7 +2721,7 @@
         <v>176</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>26</v>
+        <v>217</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="28.8">
@@ -2757,30 +2757,30 @@
       </c>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="B21" s="23"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23"/>
-      <c r="J21" s="24"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="22"/>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="25"/>
-      <c r="B22" s="26"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="26"/>
-      <c r="I22" s="26"/>
-      <c r="J22" s="27"/>
+      <c r="A22" s="23"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="25"/>
     </row>
     <row r="23" spans="1:13" ht="28.8">
       <c r="A23" s="13">
@@ -2847,30 +2847,30 @@
       </c>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="24"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="22"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="25"/>
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="27"/>
+      <c r="A26" s="23"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="25"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="13">
@@ -3013,6 +3013,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
